--- a/finance dashboard.xlsx
+++ b/finance dashboard.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRATYUSH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DB82C2B-A707-4581-AD57-7F12A45782FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAA58C3-021A-4625-9227-43302D25CF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C695B0BC-3BF1-49AE-932D-A2988AAA7F15}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Dashboard 1" sheetId="2" r:id="rId1"/>
+    <sheet name="Dashboard 2" sheetId="3" r:id="rId2"/>
+    <sheet name="Stock prices" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet2!$T$11:$T$14</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet2!$AC$10:$AC$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet2!$A$1:$W$73</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Dashboard 1'!$T$11:$T$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard 1'!$A$1:$W$73</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="223">
   <si>
     <t>Revenue</t>
   </si>
@@ -822,6 +821,92 @@
   <si>
     <t>Var%</t>
   </si>
+  <si>
+    <t>Projected Business Performance</t>
+  </si>
+  <si>
+    <t>Apple inc</t>
+  </si>
+  <si>
+    <t>Apple Inc. is a premier American technology company founded in 1976 by Steve Jobs, Steve Wozniak, and Ronald Wayne, headquartered in Cupertino, California. Renowned for innovation, it designs consumer electronics (iPhone, Mac, iPad, Watch), software (iOS, macOS), and services (iCloud, Apple Pay). As a global leader, it emphasizes design, ecosystem integration, and user privacy.</t>
+  </si>
+  <si>
+    <t>Recomendation : Buy</t>
+  </si>
+  <si>
+    <t>Stock Chart: Trailing 52-Weeks</t>
+  </si>
+  <si>
+    <t>Valuation Summary: Football Field Chart</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Total Revenue </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t>(US$ Millions)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Other Financial Metrics </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t>(US$ Millions)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  PROFITABILITY  ($M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  GROWTH METRICS</t>
+  </si>
+  <si>
+    <t>Revenue YoY Growth (%)</t>
+  </si>
+  <si>
+    <t>EBITDA YoY Growth (%)</t>
+  </si>
+  <si>
+    <t>Net Income YoY Growth (%)</t>
+  </si>
+  <si>
+    <t>Target price</t>
+  </si>
+  <si>
+    <t>APPLE INC</t>
+  </si>
+  <si>
+    <t>Company name</t>
+  </si>
 </sst>
 </file>
 
@@ -840,11 +925,11 @@
     <numFmt numFmtId="173" formatCode="&quot;+$&quot;#,##0.00;&quot;-$&quot;#,##0.00;\-"/>
     <numFmt numFmtId="174" formatCode="\+0.0%;\-0.0%;\-"/>
     <numFmt numFmtId="175" formatCode="0&quot;A&quot;"/>
-    <numFmt numFmtId="181" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="182" formatCode="\⬆\️_(#,##0.0%_);\⬇\️\(#,##0.0%\);_(&quot;–&quot;_);_(@_)"/>
-    <numFmt numFmtId="183" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="177" formatCode="\⬆\️_(#,##0.0%_);\⬇\️\(#,##0.0%\);_(&quot;–&quot;_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="57" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1159,6 +1244,66 @@
       <name val="Open Sans"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF3271D2"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1337,7 +1482,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="37" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1482,18 +1627,6 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1632,19 +1765,16 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1653,10 +1783,6 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1706,22 +1832,19 @@
     <xf numFmtId="169" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1733,7 +1856,7 @@
     <xf numFmtId="166" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1748,11 +1871,108 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="7" fillId="11" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="11" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1764,82 +1984,7 @@
     <cellStyle name="Percent" xfId="6" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="3" xr:uid="{625D2891-B30A-4C97-89E8-04620D32FC47}"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FF3271D2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFEB6105"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FF3271D2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFEB6105"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFEB6105"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FF3271D2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFEB6105"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FF3271D2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FF3271D2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFEB6105"/>
-      </font>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1964,7 +2109,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$11</c:f>
+              <c:f>'Dashboard 1'!$O$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2015,11 +2160,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$11:$W$11</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$11:$W$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$11:$T$11</c:f>
+              <c:f>'Dashboard 1'!$P$11:$T$11</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2052,7 +2197,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$12</c:f>
+              <c:f>'Dashboard 1'!$O$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2101,11 +2246,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$12:$W$12</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$12:$W$12</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$12:$T$12</c:f>
+              <c:f>'Dashboard 1'!$P$12:$T$12</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2138,7 +2283,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$13</c:f>
+              <c:f>'Dashboard 1'!$O$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2189,11 +2334,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$13:$W$13</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$13:$W$13</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$13:$T$13</c:f>
+              <c:f>'Dashboard 1'!$P$13:$T$13</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2244,7 +2389,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$O$10</c15:sqref>
+                          <c15:sqref>'Dashboard 1'!$O$10</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2273,10 +2418,10 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>Sheet2!$P$10:$W$10</c15:sqref>
+                          <c15:sqref>'Dashboard 1'!$P$10:$W$10</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$P$10:$T$10</c15:sqref>
+                          <c15:sqref>'Dashboard 1'!$P$10:$T$10</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2319,7 +2464,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$14</c:f>
+              <c:f>'Dashboard 1'!$O$14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2427,11 +2572,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$14:$W$14</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$14:$W$14</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$14:$T$14</c:f>
+              <c:f>'Dashboard 1'!$P$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2720,7 +2865,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$18</c:f>
+              <c:f>'Dashboard 1'!$O$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2771,11 +2916,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$18:$W$18</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$18:$W$18</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$18:$T$18</c:f>
+              <c:f>'Dashboard 1'!$P$18:$T$18</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2824,7 +2969,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$19</c:f>
+              <c:f>'Dashboard 1'!$O$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2916,19 +3061,19 @@
             <c:strLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>100.0%</c:v>
+                <c:v>1</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>200.0%</c:v>
+                <c:v>2</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>300.0%</c:v>
+                <c:v>3</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>400.0%</c:v>
+                <c:v>4</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>500.0%</c:v>
+                <c:v>5</c:v>
               </c:pt>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
@@ -2942,11 +3087,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$19:$W$19</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$19:$W$19</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$19:$T$19</c:f>
+              <c:f>'Dashboard 1'!$P$19:$T$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%;\(0.0%\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3245,7 +3390,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$22</c:f>
+              <c:f>'Dashboard 1'!$O$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3270,11 +3415,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$8:$T$8</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$8:$T$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$8:$T$8</c:f>
+              <c:f>'Dashboard 1'!$P$8:$T$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -3300,11 +3445,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$22:$W$22</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$22:$W$22</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$22:$T$22</c:f>
+              <c:f>'Dashboard 1'!$P$22:$T$22</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3337,7 +3482,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$O$23</c:f>
+              <c:f>'Dashboard 1'!$O$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3363,11 +3508,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$8:$T$8</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$8:$T$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$8:$T$8</c:f>
+              <c:f>'Dashboard 1'!$P$8:$T$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -3393,11 +3538,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet2!$P$23:$W$23</c15:sqref>
+                    <c15:sqref>'Dashboard 1'!$P$23:$W$23</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet2!$P$23:$T$23</c:f>
+              <c:f>'Dashboard 1'!$P$23:$T$23</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3624,46 +3769,27 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
+        <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$X$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Low</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -3674,9 +3800,90 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$3:$V$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>52-Week Trading Range</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Consensus Research Target</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Precedent Transactions (EV)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sum-of-the-Parts (SOTP)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Discounted Cash Flow (DCF)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet3!$AD$3:$AD$7</c:f>
+              <c:f>'Dashboard 2'!$X$3:$X$7</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3707,6 +3914,17 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$Y$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2"/>
@@ -3717,9 +3935,90 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$3:$V$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>52-Week Trading Range</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Consensus Research Target</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Precedent Transactions (EV)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sum-of-the-Parts (SOTP)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Discounted Cash Flow (DCF)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet3!$AE$3:$AE$7</c:f>
+              <c:f>'Dashboard 2'!$Y$3:$Y$7</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3750,6 +4049,17 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$Z$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>High</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent3"/>
@@ -3760,9 +4070,90 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$3:$V$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>52-Week Trading Range</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Consensus Research Target</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Precedent Transactions (EV)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sum-of-the-Parts (SOTP)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Discounted Cash Flow (DCF)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet3!$AF$3:$AF$7</c:f>
+              <c:f>'Dashboard 2'!$Z$3:$Z$7</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3791,14 +4182,16 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
+        <c:overlap val="100"/>
         <c:axId val="506414336"/>
         <c:axId val="506417216"/>
       </c:barChart>
@@ -3809,6 +4202,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3859,20 +4253,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="\$#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3963,12 +4343,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -3992,6 +4367,1659 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stock prices'!$A$6:$A$57</c:f>
+              <c:strCache>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>Feb 28, 2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb 21, 2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Feb 14, 2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Feb 07, 2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jan 31, 2026</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jan 24, 2026</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jan 17, 2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Jan 10, 2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Jan 03, 2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Dec 27, 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Dec 20, 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec 13, 2025</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Dec 06, 2025</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Nov 29, 2025</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Nov 22, 2025</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Nov 15, 2025</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Nov 08, 2025</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Nov 01, 2025</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Oct 25, 2025</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Oct 18, 2025</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Oct 11, 2025</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Oct 04, 2025</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Sep 27, 2025</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Sep 20, 2025</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Sep 13, 2025</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Sep 06, 2025</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Aug 30, 2025</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Aug 23, 2025</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Aug 16, 2025</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Aug 09, 2025</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Aug 02, 2025</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Jul 26, 2025</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Jul 19, 2025</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Jul 12, 2025</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Jul 05, 2025</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Jun 28, 2025</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Jun 21, 2025</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Jun 14, 2025</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Jun 07, 2025</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>May 31, 2025</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>May 24, 2025</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>May 17, 2025</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>May 10, 2025</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>May 03, 2025</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Apr 26, 2025</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Apr 19, 2025</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Apr 12, 2025</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Apr 05, 2025</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Mar 29, 2025</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Mar 22, 2025</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Mar 15, 2025</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>Mar 08, 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stock prices'!$E$6:$E$57</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00;\(#,##0.00\);\-</c:formatCode>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>264.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>264.58</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>277.86</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>275.91000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>259.48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>255.41</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>248.04</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>259.37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>267.26</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>273.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>271.86</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>284.14999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>278.77999999999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>237.33</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>232.15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>224.23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>222.91</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>225.91</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>230.76</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>222.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>229.04</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>226.78</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>227.52</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>220.11</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>222.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>220.82</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>226.84</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>219.86</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>208.14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>196.89</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>210.62</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>217.96</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>207.52</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>210.96</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>198.15</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>199.49</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>205.75</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>207.16</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>200.63</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>193.42</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>192.35</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>205.62</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>188.38</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>176.62</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>165.44</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>185.12</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>170.38</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>216.83</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>214.29</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>213.49</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>213.49</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9E35-427E-8D5B-EADF075F5773}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1206844112"/>
+        <c:axId val="1206848912"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1206844112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mm/yyyy" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1206848912"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1206848912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0.00;\(#,##0.00\);\-" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1206844112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>EBITDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="63500" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$X$34:$AE$34</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>FY2020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>FY2025E</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>FY2026E</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>FY2027E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard 2'!$W$28:$AC$28</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="1">
+                  <c:v>77566</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120233</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>131768</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>125820</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>134661</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>138729</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5819-4554-99CA-37AB8E113D99}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$30</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Net Income</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="69850" cap="sq">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="plus"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln w="3175" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$X$34:$AE$34</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>FY2020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>FY2025E</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>FY2026E</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>FY2027E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard 2'!$W$30:$AC$30</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="1">
+                  <c:v>57411</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>94680</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>99803</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>96995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93736</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>97485</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5819-4554-99CA-37AB8E113D99}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="504587600"/>
+        <c:axId val="504592880"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="504587600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="504592880"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="504592880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="504587600"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12527499553739663"/>
+          <c:y val="0.11892003576730414"/>
+          <c:w val="0.79020567643150397"/>
+          <c:h val="0.75231141862504236"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>iPhone</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$X$34:$AE$34</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>FY2020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>FY2025E</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>FY2026E</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>FY2027E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard 2'!$W$36:$AE$36</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="1">
+                  <c:v>28622</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35190</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40177</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29357</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29984</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31783.040000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33690.022400000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>35711.423744000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C782-420D-B49C-DEB294B9C5AD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Services</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$X$34:$AE$34</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>FY2020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>FY2025E</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>FY2026E</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>FY2027E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard 2'!$W$37:$AE$37</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="1">
+                  <c:v>53768</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68425</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78129</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>96169</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>107709.28000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120634.39360000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>135110.52083200004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C782-420D-B49C-DEB294B9C5AD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mac + iPad + Wearables</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$X$34:$AE$34</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>FY2020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>FY2025E</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>FY2026E</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>FY2027E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard 2'!$W$38:$AE$38</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="1">
+                  <c:v>82966</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>105708</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110711</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>97502</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93683</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>96493.49</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>99388.294700000013</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>102369.94354100002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C782-420D-B49C-DEB294B9C5AD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="100"/>
+        <c:axId val="1097841200"/>
+        <c:axId val="1097841680"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Dashboard 2'!$V$57</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue YoY Growth (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard 2'!$W$57:$AE$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="2" formatCode="0.0%;\(0.0%\);\-">
+                  <c:v>0.39331983364905176</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0%;\(0.0%\);\-">
+                  <c:v>7.0405734139696724E-2</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0%;\(0.0%\);\-">
+                  <c:v>-2.3874757286278098E-2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0%;\(0.0%\);\-">
+                  <c:v>2.9912804175827464E-3</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.0%;\(0.0%\);\-">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.0%;\(0.0%\);\-">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.0%;\(0.0%\);\-">
+                  <c:v>4.0000000000000077E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C782-420D-B49C-DEB294B9C5AD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1097867120"/>
+        <c:axId val="1097862320"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1097841200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1097841680"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1097841680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1097841200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:dispUnits>
+          <c:builtInUnit val="thousands"/>
+          <c:dispUnitsLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+          </c:dispUnitsLbl>
+        </c:dispUnits>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1097862320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1097867120"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1097867120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1097862320"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4058,7 +6086,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet4!$A$6:$A$57</c:f>
+              <c:f>'Stock prices'!$A$6:$A$57</c:f>
               <c:strCache>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
@@ -4222,937 +6250,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$E$6:$E$57</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00;\(#,##0.00\);\-</c:formatCode>
-                <c:ptCount val="52"/>
-                <c:pt idx="0">
-                  <c:v>264.18</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>264.58</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>277.86</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>275.91000000000003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>259.48</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>255.41</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>248.04</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>259.37</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>267.26</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>273.39999999999998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>271.86</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>284.14999999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>278.77999999999997</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>237.33</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>232.15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>229</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>224.23</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>222.91</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>225.91</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>230.76</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>222.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>229.04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>226.78</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>227.52</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>220.11</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>222.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>220.82</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>226.84</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>219.86</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>208.14</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>196.89</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>210.62</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>217.96</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>207.52</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>210.96</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>198.15</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>199.49</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>205.75</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>207.16</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>200.63</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>193.42</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>192.35</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>205.62</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>188.38</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>176.62</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>165.44</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>185.12</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>170.38</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>216.83</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>214.29</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>213.49</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>213.49</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9E35-427E-8D5B-EADF075F5773}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1206844112"/>
-        <c:axId val="1206848912"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1206844112"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1206848912"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1206848912"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.00;\(#,##0.00\);\-" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1206844112"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet3!$AB$28</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>EBITDA</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet3!$AC$28:$AI$28</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="1">
-                  <c:v>77566</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>120233</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>131768</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>125820</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>134661</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>138729</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5819-4554-99CA-37AB8E113D99}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet3!$AB$30</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Net Income</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet3!$AC$30:$AI$30</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="1">
-                  <c:v>57411</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>94680</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>99803</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>96995</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>93736</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>97485</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5819-4554-99CA-37AB8E113D99}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="504587600"/>
-        <c:axId val="504592880"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="504587600"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="504592880"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="504592880"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="504587600"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet4!$A$6:$A$57</c:f>
-              <c:strCache>
-                <c:ptCount val="52"/>
-                <c:pt idx="0">
-                  <c:v>Feb 28, 2026</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Feb 21, 2026</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Feb 14, 2026</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Feb 07, 2026</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Jan 31, 2026</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Jan 24, 2026</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Jan 17, 2026</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Jan 10, 2026</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Jan 03, 2026</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Dec 27, 2025</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Dec 20, 2025</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Dec 13, 2025</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Dec 06, 2025</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Nov 29, 2025</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Nov 22, 2025</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Nov 15, 2025</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Nov 08, 2025</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Nov 01, 2025</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Oct 25, 2025</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Oct 18, 2025</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Oct 11, 2025</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Oct 04, 2025</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Sep 27, 2025</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Sep 20, 2025</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Sep 13, 2025</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>Sep 06, 2025</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Aug 30, 2025</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Aug 23, 2025</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Aug 16, 2025</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Aug 09, 2025</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>Aug 02, 2025</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>Jul 26, 2025</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>Jul 19, 2025</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>Jul 12, 2025</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>Jul 05, 2025</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>Jun 28, 2025</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>Jun 21, 2025</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>Jun 14, 2025</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>Jun 07, 2025</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>May 31, 2025</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>May 24, 2025</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>May 17, 2025</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>May 10, 2025</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>May 03, 2025</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>Apr 26, 2025</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>Apr 19, 2025</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>Apr 12, 2025</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>Apr 05, 2025</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>Mar 29, 2025</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>Mar 22, 2025</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>Mar 15, 2025</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>Mar 08, 2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet4!$E$6:$E$57</c:f>
+              <c:f>'Stock prices'!$E$6:$E$57</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00;\(#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="52"/>
@@ -5874,6 +6972,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -9449,6 +10587,509 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10121,8 +11762,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="535966" y="4776020"/>
-              <a:ext cx="5266957" cy="2221525"/>
+              <a:off x="535966" y="4887975"/>
+              <a:ext cx="5251717" cy="2311793"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -10210,16 +11851,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>441960</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>554849</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>77611</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>7054</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>7056</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10249,15 +11890,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:colOff>536222</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>130387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>49389</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>31608</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10286,16 +11927,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>532931</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>48163</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>593067</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>92716</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10322,6 +11963,93 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>101599</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>179211</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>747890</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3804C179-8043-8742-73D4-135DB0665824}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:lum bright="70000" contrast="-70000"/>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="101599" y="63500"/>
+          <a:ext cx="684390" cy="684390"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>523272</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>63137</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>78772</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>36073</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F590C804-CD89-E51F-6A78-4ACFB8B2EF17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10329,16 +12057,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10663,105 +12391,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C54E12-7867-40B5-B19F-47AA1C89772F}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:W143"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="109"/>
-    <col min="2" max="2" width="8.88671875" style="109" customWidth="1"/>
-    <col min="3" max="3" width="32" style="109" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="109" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="109" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" style="109" customWidth="1"/>
-    <col min="7" max="9" width="8.88671875" style="109"/>
-    <col min="10" max="10" width="9.77734375" style="109" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="109" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.77734375" style="109" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="109" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="109"/>
-    <col min="15" max="15" width="61.21875" style="109" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.88671875" style="109" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.44140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.88671875" style="109" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="10.44140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.88671875" style="109" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.44140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.77734375" style="109" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="109"/>
+    <col min="1" max="1" width="8.88671875" style="105"/>
+    <col min="2" max="2" width="8.88671875" style="105" customWidth="1"/>
+    <col min="3" max="3" width="32" style="105" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="105" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" style="105" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" style="105" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="105"/>
+    <col min="10" max="10" width="9.77734375" style="105" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="105" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.77734375" style="105" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="105" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="105"/>
+    <col min="15" max="15" width="61.21875" style="105" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" style="105" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.44140625" style="105" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.88671875" style="105" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.44140625" style="105" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.88671875" style="105" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.44140625" style="105" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.77734375" style="105" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="105"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="47.4" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A1" s="105"/>
-      <c r="B1" s="105"/>
-      <c r="C1" s="106" t="s">
+      <c r="A1" s="101"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="102" t="s">
         <v>191</v>
       </c>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="108" t="s">
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O2" s="110"/>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="110"/>
-      <c r="S2" s="110"/>
-      <c r="T2" s="110"/>
-      <c r="U2" s="110"/>
-      <c r="V2" s="110"/>
-      <c r="W2" s="110"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="104"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
     </row>
     <row r="3" spans="1:23" ht="21" x14ac:dyDescent="0.35">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="92" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="O3" s="111" t="s">
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="O3" s="106" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="21" x14ac:dyDescent="0.35">
-      <c r="B4" s="98"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="O4" s="111"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="O4" s="106"/>
     </row>
     <row r="5" spans="1:23" ht="21" x14ac:dyDescent="0.35">
       <c r="B5" s="6"/>
@@ -10775,16 +12506,16 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="103" t="s">
+      <c r="M5" s="99" t="s">
         <v>189</v>
       </c>
-      <c r="O5" s="111"/>
+      <c r="O5" s="106"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O6" s="111"/>
+      <c r="O6" s="106"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O7" s="111"/>
+      <c r="O7" s="106"/>
     </row>
     <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
@@ -10794,40 +12525,40 @@
       <c r="D8" s="49"/>
       <c r="E8" s="49"/>
       <c r="F8" s="49"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="147" t="s">
+      <c r="G8" s="100"/>
+      <c r="H8" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="147"/>
-      <c r="J8" s="147"/>
-      <c r="K8" s="147"/>
-      <c r="L8" s="147"/>
-      <c r="M8" s="147"/>
-      <c r="O8" s="112" t="s">
+      <c r="I8" s="165"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="165"/>
+      <c r="L8" s="165"/>
+      <c r="M8" s="165"/>
+      <c r="O8" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="P8" s="113" t="s">
+      <c r="P8" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="113" t="s">
+      <c r="Q8" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="R8" s="113" t="s">
+      <c r="R8" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="S8" s="113" t="s">
+      <c r="S8" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="T8" s="113" t="s">
+      <c r="T8" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="113" t="s">
+      <c r="U8" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="V8" s="113" t="s">
+      <c r="V8" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="W8" s="113" t="s">
+      <c r="W8" s="108" t="s">
         <v>33</v>
       </c>
     </row>
@@ -10837,378 +12568,375 @@
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="O9" s="115" t="s">
+      <c r="O9" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="P9" s="115"/>
-      <c r="Q9" s="115"/>
-      <c r="R9" s="115"/>
-      <c r="S9" s="115"/>
-      <c r="T9" s="115"/>
-      <c r="U9" s="115"/>
-      <c r="V9" s="115"/>
-      <c r="W9" s="115"/>
+      <c r="P9" s="167"/>
+      <c r="Q9" s="167"/>
+      <c r="R9" s="167"/>
+      <c r="S9" s="167"/>
+      <c r="T9" s="167"/>
+      <c r="U9" s="167"/>
+      <c r="V9" s="167"/>
+      <c r="W9" s="167"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O10" s="116" t="s">
+      <c r="O10" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="110">
         <v>137781</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="110">
         <v>191973</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="110">
         <v>205489</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="110">
         <v>200583</v>
       </c>
-      <c r="T10" s="117">
+      <c r="T10" s="110">
         <v>201183</v>
       </c>
-      <c r="U10" s="118">
+      <c r="U10" s="111">
         <f>T10*(1+0.04)</f>
         <v>209230.32</v>
       </c>
-      <c r="V10" s="118">
+      <c r="V10" s="111">
         <f>U10*(1+0.04)</f>
         <v>217599.53280000002</v>
       </c>
-      <c r="W10" s="118">
+      <c r="W10" s="111">
         <f>V10*(1+0.04)</f>
         <v>226303.51411200003</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O11" s="116" t="s">
+      <c r="O11" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="P11" s="117">
+      <c r="P11" s="110">
         <v>28622</v>
       </c>
-      <c r="Q11" s="117">
+      <c r="Q11" s="110">
         <v>35190</v>
       </c>
-      <c r="R11" s="117">
+      <c r="R11" s="110">
         <v>40177</v>
       </c>
-      <c r="S11" s="117">
+      <c r="S11" s="110">
         <v>29357</v>
       </c>
-      <c r="T11" s="117">
+      <c r="T11" s="110">
         <v>29984</v>
       </c>
-      <c r="U11" s="118">
+      <c r="U11" s="111">
         <f>T11*(1+0.06)</f>
         <v>31783.040000000001</v>
       </c>
-      <c r="V11" s="118">
+      <c r="V11" s="111">
         <f>U11*(1+0.06)</f>
         <v>33690.022400000002</v>
       </c>
-      <c r="W11" s="118">
+      <c r="W11" s="111">
         <f>V11*(1+0.06)</f>
         <v>35711.423744000007</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O12" s="116" t="s">
+      <c r="O12" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="119">
+      <c r="P12" s="112">
         <v>53768</v>
       </c>
-      <c r="Q12" s="119">
+      <c r="Q12" s="112">
         <v>68425</v>
       </c>
-      <c r="R12" s="119">
+      <c r="R12" s="112">
         <v>78129</v>
       </c>
-      <c r="S12" s="119">
+      <c r="S12" s="112">
         <v>85200</v>
       </c>
-      <c r="T12" s="119">
+      <c r="T12" s="112">
         <v>96169</v>
       </c>
-      <c r="U12" s="120">
+      <c r="U12" s="113">
         <f>T12*(1+0.12)</f>
         <v>107709.28000000001</v>
       </c>
-      <c r="V12" s="120">
+      <c r="V12" s="113">
         <f>U12*(1+0.12)</f>
         <v>120634.39360000002</v>
       </c>
-      <c r="W12" s="120">
+      <c r="W12" s="113">
         <f>V12*(1+0.12)</f>
         <v>135110.52083200004</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O13" s="116" t="s">
+      <c r="O13" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="P13" s="119">
+      <c r="P13" s="112">
         <v>82966</v>
       </c>
-      <c r="Q13" s="119">
+      <c r="Q13" s="112">
         <v>105708</v>
       </c>
-      <c r="R13" s="119">
+      <c r="R13" s="112">
         <v>110711</v>
       </c>
-      <c r="S13" s="119">
+      <c r="S13" s="112">
         <v>97502</v>
       </c>
-      <c r="T13" s="119">
+      <c r="T13" s="112">
         <v>93683</v>
       </c>
-      <c r="U13" s="120">
+      <c r="U13" s="113">
         <f>T13*(1+0.03)</f>
         <v>96493.49</v>
       </c>
-      <c r="V13" s="120">
+      <c r="V13" s="113">
         <f>U13*(1+0.03)</f>
         <v>99388.294700000013</v>
       </c>
-      <c r="W13" s="120">
+      <c r="W13" s="113">
         <f>V13*(1+0.03)</f>
         <v>102369.94354100002</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O14" s="121" t="s">
+      <c r="O14" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="P14" s="122">
+      <c r="P14" s="115">
         <f t="shared" ref="P14:W14" si="0">SUM(P11:P13)</f>
         <v>165356</v>
       </c>
-      <c r="Q14" s="122">
+      <c r="Q14" s="115">
         <f t="shared" si="0"/>
         <v>209323</v>
       </c>
-      <c r="R14" s="122">
+      <c r="R14" s="115">
         <f t="shared" si="0"/>
         <v>229017</v>
       </c>
-      <c r="S14" s="122">
+      <c r="S14" s="115">
         <f>SUM(S11:S13)</f>
         <v>212059</v>
       </c>
-      <c r="T14" s="122">
+      <c r="T14" s="115">
         <f>SUM(T11:T13)</f>
         <v>219836</v>
       </c>
-      <c r="U14" s="122">
+      <c r="U14" s="115">
         <f>SUM(U11:U13)</f>
         <v>235985.81</v>
       </c>
-      <c r="V14" s="122">
+      <c r="V14" s="115">
         <f t="shared" si="0"/>
         <v>253712.71070000005</v>
       </c>
-      <c r="W14" s="122">
+      <c r="W14" s="115">
         <f t="shared" si="0"/>
         <v>273191.88811700005</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O16" s="115" t="s">
+      <c r="O16" s="167" t="s">
         <v>39</v>
       </c>
-      <c r="P16" s="115"/>
-      <c r="Q16" s="115"/>
-      <c r="R16" s="115"/>
-      <c r="S16" s="115"/>
-      <c r="T16" s="115"/>
-      <c r="U16" s="115"/>
-      <c r="V16" s="115"/>
-      <c r="W16" s="115"/>
+      <c r="P16" s="167"/>
+      <c r="Q16" s="167"/>
+      <c r="R16" s="167"/>
+      <c r="S16" s="167"/>
+      <c r="T16" s="167"/>
+      <c r="U16" s="167"/>
+      <c r="V16" s="167"/>
+      <c r="W16" s="167"/>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O17" s="116" t="s">
+      <c r="O17" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="P17" s="117">
+      <c r="P17" s="110">
         <v>169559</v>
       </c>
-      <c r="Q17" s="117">
+      <c r="Q17" s="110">
         <v>212981</v>
       </c>
-      <c r="R17" s="117">
+      <c r="R17" s="110">
         <v>223546</v>
       </c>
-      <c r="S17" s="117">
+      <c r="S17" s="110">
         <v>214137</v>
       </c>
-      <c r="T17" s="117">
+      <c r="T17" s="110">
         <v>210352</v>
       </c>
-      <c r="U17" s="118">
+      <c r="U17" s="111">
         <f>U14*(1-0.462)</f>
         <v>126960.36578000001</v>
       </c>
-      <c r="V17" s="118">
+      <c r="V17" s="111">
         <f>V14*(1-0.455)</f>
         <v>138273.42733150002</v>
       </c>
-      <c r="W17" s="118">
+      <c r="W17" s="111">
         <f>W14*(1-0.45)</f>
         <v>150255.53846435004</v>
       </c>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O18" s="123" t="s">
+      <c r="O18" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="P18" s="124">
+      <c r="P18" s="117">
         <f t="shared" ref="P18:W18" si="1">P14-P17</f>
         <v>-4203</v>
       </c>
-      <c r="Q18" s="124">
+      <c r="Q18" s="117">
         <f t="shared" si="1"/>
         <v>-3658</v>
       </c>
-      <c r="R18" s="124">
+      <c r="R18" s="117">
         <f t="shared" si="1"/>
         <v>5471</v>
       </c>
-      <c r="S18" s="124">
+      <c r="S18" s="117">
         <f>S14-S17</f>
         <v>-2078</v>
       </c>
-      <c r="T18" s="124">
+      <c r="T18" s="117">
         <f>T14-T17</f>
         <v>9484</v>
       </c>
-      <c r="U18" s="124">
+      <c r="U18" s="117">
         <f>U14-U17</f>
         <v>109025.44421999999</v>
       </c>
-      <c r="V18" s="124">
+      <c r="V18" s="117">
         <f t="shared" si="1"/>
         <v>115439.28336850004</v>
       </c>
-      <c r="W18" s="124">
+      <c r="W18" s="117">
         <f t="shared" si="1"/>
         <v>122936.34965265001</v>
       </c>
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O19" s="125" t="s">
+      <c r="O19" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="P19" s="126">
+      <c r="P19" s="119">
         <f>IFERROR(P18/P14,"-")</f>
         <v>-2.541788625752921E-2</v>
       </c>
-      <c r="Q19" s="126">
+      <c r="Q19" s="119">
         <f t="shared" ref="Q19:W19" si="2">IFERROR(Q18/Q14,"-")</f>
         <v>-1.7475384931421773E-2</v>
       </c>
-      <c r="R19" s="126">
+      <c r="R19" s="119">
         <f t="shared" si="2"/>
         <v>2.3889056270931852E-2</v>
       </c>
-      <c r="S19" s="126">
+      <c r="S19" s="119">
         <f t="shared" si="2"/>
         <v>-9.7991596678282927E-3</v>
       </c>
-      <c r="T19" s="126">
+      <c r="T19" s="119">
         <f t="shared" si="2"/>
         <v>4.3141250750559509E-2</v>
       </c>
-      <c r="U19" s="126">
+      <c r="U19" s="119">
         <f t="shared" si="2"/>
         <v>0.46199999999999997</v>
       </c>
-      <c r="V19" s="126">
+      <c r="V19" s="119">
         <f t="shared" si="2"/>
         <v>0.45500000000000007</v>
       </c>
-      <c r="W19" s="126">
+      <c r="W19" s="119">
         <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="21" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O21" s="115" t="s">
+      <c r="O21" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="115"/>
-      <c r="R21" s="115"/>
-      <c r="S21" s="115"/>
-      <c r="T21" s="115"/>
-      <c r="U21" s="115"/>
-      <c r="V21" s="115"/>
-      <c r="W21" s="115"/>
+      <c r="P21" s="167"/>
+      <c r="Q21" s="167"/>
+      <c r="R21" s="167"/>
+      <c r="S21" s="167"/>
+      <c r="T21" s="167"/>
+      <c r="U21" s="167"/>
+      <c r="V21" s="167"/>
+      <c r="W21" s="167"/>
     </row>
     <row r="22" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O22" s="116" t="s">
+      <c r="O22" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="P22" s="117">
+      <c r="P22" s="110">
         <v>18752</v>
       </c>
-      <c r="Q22" s="117">
+      <c r="Q22" s="110">
         <v>21914</v>
       </c>
-      <c r="R22" s="117">
+      <c r="R22" s="110">
         <v>26251</v>
       </c>
-      <c r="S22" s="117">
+      <c r="S22" s="110">
         <v>29915</v>
       </c>
-      <c r="T22" s="117">
+      <c r="T22" s="110">
         <v>31370</v>
       </c>
-      <c r="U22" s="118">
+      <c r="U22" s="111">
         <f t="shared" ref="U22:W23" si="3">T22*(1+0.06)</f>
         <v>33252.200000000004</v>
       </c>
-      <c r="V22" s="118">
+      <c r="V22" s="111">
         <f t="shared" si="3"/>
         <v>35247.332000000009</v>
       </c>
-      <c r="W22" s="118">
+      <c r="W22" s="111">
         <f t="shared" si="3"/>
         <v>37362.171920000015</v>
       </c>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O23" s="116" t="s">
+      <c r="O23" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="P23" s="117">
+      <c r="P23" s="110">
         <v>19916</v>
       </c>
-      <c r="Q23" s="117">
+      <c r="Q23" s="110">
         <v>21973</v>
       </c>
-      <c r="R23" s="117">
+      <c r="R23" s="110">
         <v>25094</v>
       </c>
-      <c r="S23" s="117">
+      <c r="S23" s="110">
         <v>24932</v>
       </c>
-      <c r="T23" s="117">
+      <c r="T23" s="110">
         <v>26097</v>
       </c>
-      <c r="U23" s="118">
+      <c r="U23" s="111">
         <f t="shared" si="3"/>
         <v>27662.82</v>
       </c>
-      <c r="V23" s="118">
+      <c r="V23" s="111">
         <f t="shared" si="3"/>
         <v>29322.589200000002</v>
       </c>
-      <c r="W23" s="118">
+      <c r="W23" s="111">
         <f t="shared" si="3"/>
         <v>31081.944552000004</v>
       </c>
@@ -11229,184 +12957,184 @@
       <c r="K24" s="49"/>
       <c r="L24" s="49"/>
       <c r="M24" s="49"/>
-      <c r="O24" s="123" t="s">
+      <c r="O24" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="P24" s="124">
+      <c r="P24" s="117">
         <f t="shared" ref="P24:W24" si="4">SUM(P22:P23)</f>
         <v>38668</v>
       </c>
-      <c r="Q24" s="124">
+      <c r="Q24" s="117">
         <f t="shared" si="4"/>
         <v>43887</v>
       </c>
-      <c r="R24" s="124">
+      <c r="R24" s="117">
         <f t="shared" si="4"/>
         <v>51345</v>
       </c>
-      <c r="S24" s="124">
+      <c r="S24" s="117">
         <f t="shared" si="4"/>
         <v>54847</v>
       </c>
-      <c r="T24" s="124">
+      <c r="T24" s="117">
         <f t="shared" si="4"/>
         <v>57467</v>
       </c>
-      <c r="U24" s="124">
+      <c r="U24" s="117">
         <f>SUM(U22:U23)</f>
         <v>60915.020000000004</v>
       </c>
-      <c r="V24" s="124">
+      <c r="V24" s="117">
         <f t="shared" si="4"/>
         <v>64569.921200000012</v>
       </c>
-      <c r="W24" s="124">
+      <c r="W24" s="117">
         <f t="shared" si="4"/>
         <v>68444.116472000023</v>
       </c>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O26" s="108" t="s">
+      <c r="O26" s="166" t="s">
         <v>47</v>
       </c>
-      <c r="P26" s="108"/>
-      <c r="Q26" s="108"/>
-      <c r="R26" s="108"/>
-      <c r="S26" s="108"/>
+      <c r="P26" s="166"/>
+      <c r="Q26" s="166"/>
+      <c r="R26" s="166"/>
+      <c r="S26" s="166"/>
     </row>
     <row r="27" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O27" s="111" t="s">
+      <c r="O27" s="106" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O29" s="112" t="s">
+      <c r="O29" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="P29" s="113" t="s">
+      <c r="P29" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="Q29" s="113" t="s">
+      <c r="Q29" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="R29" s="113" t="s">
+      <c r="R29" s="108" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O30" s="115" t="s">
+      <c r="O30" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="P30" s="115"/>
-      <c r="Q30" s="115"/>
-      <c r="R30" s="115"/>
-      <c r="S30" s="115"/>
+      <c r="P30" s="167"/>
+      <c r="Q30" s="167"/>
+      <c r="R30" s="167"/>
+      <c r="S30" s="167"/>
     </row>
     <row r="31" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O31" s="123" t="s">
+      <c r="O31" s="116" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="O32" s="116" t="s">
+      <c r="O32" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="P32" s="117">
+      <c r="P32" s="110">
         <v>23646</v>
       </c>
-      <c r="Q32" s="117">
+      <c r="Q32" s="110">
         <v>29965</v>
       </c>
-      <c r="R32" s="117">
+      <c r="R32" s="110">
         <v>29943</v>
       </c>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="O33" s="116" t="s">
+      <c r="O33" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="P33" s="117">
+      <c r="P33" s="110">
         <v>24658</v>
       </c>
-      <c r="Q33" s="117">
+      <c r="Q33" s="110">
         <v>31590</v>
       </c>
-      <c r="R33" s="117">
+      <c r="R33" s="110">
         <v>35228</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="O34" s="116" t="s">
+      <c r="O34" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="P34" s="117">
+      <c r="P34" s="110">
         <v>28945</v>
       </c>
-      <c r="Q34" s="117">
+      <c r="Q34" s="110">
         <v>29508</v>
       </c>
-      <c r="R34" s="117">
+      <c r="R34" s="110">
         <v>33410</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="O35" s="116" t="s">
+      <c r="O35" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="P35" s="117">
+      <c r="P35" s="110">
         <v>4946</v>
       </c>
-      <c r="Q35" s="117">
+      <c r="Q35" s="110">
         <v>6331</v>
       </c>
-      <c r="R35" s="117">
+      <c r="R35" s="110">
         <v>7286</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="O36" s="116" t="s">
+      <c r="O36" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="P36" s="117">
+      <c r="P36" s="110">
         <v>21223</v>
       </c>
-      <c r="Q36" s="117">
+      <c r="Q36" s="110">
         <v>14695</v>
       </c>
-      <c r="R36" s="117">
+      <c r="R36" s="110">
         <v>14287</v>
       </c>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="O37" s="123" t="s">
+      <c r="O37" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="P37" s="127">
+      <c r="P37" s="120">
         <f>SUM(P31:P36)</f>
         <v>103418</v>
       </c>
-      <c r="Q37" s="127">
+      <c r="Q37" s="120">
         <f>SUM(Q31:Q36)</f>
         <v>112089</v>
       </c>
-      <c r="R37" s="127">
+      <c r="R37" s="120">
         <f>SUM(R31:R36)</f>
         <v>120154</v>
       </c>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="O39" s="123" t="s">
+      <c r="O39" s="116" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="40" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="56" t="s">
         <v>186</v>
       </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
       <c r="H40" s="8" t="s">
         <v>203</v>
       </c>
@@ -11415,1094 +13143,1094 @@
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
       <c r="M40" s="49"/>
-      <c r="O40" s="116" t="s">
+      <c r="O40" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="P40" s="117">
+      <c r="P40" s="110">
         <v>120805</v>
       </c>
-      <c r="Q40" s="117">
+      <c r="Q40" s="110">
         <v>100544</v>
       </c>
-      <c r="R40" s="117">
+      <c r="R40" s="110">
         <v>91478</v>
       </c>
     </row>
     <row r="41" spans="2:19" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
-      <c r="O41" s="116" t="s">
+      <c r="O41" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="P41" s="117">
+      <c r="P41" s="110">
         <v>42117</v>
       </c>
-      <c r="Q41" s="117">
+      <c r="Q41" s="110">
         <v>43715</v>
       </c>
-      <c r="R41" s="117">
+      <c r="R41" s="110">
         <v>45680</v>
       </c>
     </row>
     <row r="42" spans="2:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B42" s="61"/>
-      <c r="C42" s="74" t="s">
+      <c r="B42" s="57"/>
+      <c r="C42" s="70" t="s">
         <v>181</v>
       </c>
-      <c r="D42" s="75" t="s">
+      <c r="D42" s="71" t="s">
         <v>182</v>
       </c>
-      <c r="E42" s="75"/>
+      <c r="E42" s="71"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="54" t="s">
+      <c r="J42" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="K42" s="54" t="s">
+      <c r="K42" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="54" t="s">
+      <c r="L42" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="M42" s="54" t="s">
+      <c r="M42" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O42" s="116" t="s">
+      <c r="O42" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="P42" s="117">
+      <c r="P42" s="110">
         <v>54428</v>
       </c>
-      <c r="Q42" s="117">
+      <c r="Q42" s="110">
         <v>64758</v>
       </c>
-      <c r="R42" s="117">
+      <c r="R42" s="110">
         <v>74148</v>
       </c>
     </row>
     <row r="43" spans="2:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B43" s="71" t="s">
+      <c r="B43" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C43" s="76">
+      <c r="C43" s="72">
         <f>AVERAGE(P14:T14)</f>
         <v>207118.2</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
       <c r="H43" s="1"/>
       <c r="I43" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="J43" s="138">
+      <c r="J43" s="130">
         <f>U14</f>
         <v>235985.81</v>
       </c>
-      <c r="K43" s="139">
+      <c r="K43" s="131">
         <f>F79</f>
         <v>413876</v>
       </c>
-      <c r="L43" s="140">
+      <c r="L43" s="132">
         <f>J43-K43</f>
         <v>-177890.19</v>
       </c>
-      <c r="M43" s="141">
+      <c r="M43" s="133">
         <f>L43/K43</f>
         <v>-0.42981518619103309</v>
       </c>
-      <c r="O43" s="123" t="s">
+      <c r="O43" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="P43" s="127">
+      <c r="P43" s="120">
         <f>SUM(P40:P42)</f>
         <v>217350</v>
       </c>
-      <c r="Q43" s="127">
+      <c r="Q43" s="120">
         <f>SUM(Q40:Q42)</f>
         <v>209017</v>
       </c>
-      <c r="R43" s="127">
+      <c r="R43" s="120">
         <f>SUM(R40:R42)</f>
         <v>211306</v>
       </c>
     </row>
     <row r="44" spans="2:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B44" s="71"/>
-      <c r="C44" s="78"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="75"/>
       <c r="H44" s="1"/>
       <c r="I44" s="7"/>
-      <c r="J44" s="55"/>
-      <c r="K44" s="142"/>
-      <c r="L44" s="142"/>
-      <c r="M44" s="143"/>
-      <c r="O44" s="128" t="s">
+      <c r="J44" s="51"/>
+      <c r="K44" s="134"/>
+      <c r="L44" s="134"/>
+      <c r="M44" s="135"/>
+      <c r="O44" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="P44" s="129">
+      <c r="P44" s="122">
         <f>P37+P43</f>
         <v>320768</v>
       </c>
-      <c r="Q44" s="129">
+      <c r="Q44" s="122">
         <f>Q37+Q43</f>
         <v>321106</v>
       </c>
-      <c r="R44" s="129">
+      <c r="R44" s="122">
         <f>R37+R43</f>
         <v>331460</v>
       </c>
     </row>
     <row r="45" spans="2:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B45" s="71" t="s">
+      <c r="B45" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="72">
         <f>AVERAGE(P17:T17)</f>
         <v>206115</v>
       </c>
-      <c r="D45" s="80"/>
-      <c r="E45" s="80"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
       <c r="H45" s="1"/>
       <c r="I45" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="J45" s="138">
+      <c r="J45" s="130">
         <f>U17</f>
         <v>126960.36578000001</v>
       </c>
-      <c r="K45" s="139">
+      <c r="K45" s="131">
         <f>C118</f>
         <v>219532</v>
       </c>
-      <c r="L45" s="140">
+      <c r="L45" s="132">
         <f>J45-K45</f>
         <v>-92571.634219999993</v>
       </c>
-      <c r="M45" s="141">
+      <c r="M45" s="133">
         <f>L45/K45</f>
         <v>-0.42167717790572667</v>
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B46" s="71"/>
-      <c r="C46" s="78"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="75"/>
       <c r="H46" s="1"/>
       <c r="I46" s="7"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="142"/>
-      <c r="M46" s="143"/>
-      <c r="O46" s="115" t="s">
+      <c r="J46" s="51"/>
+      <c r="K46" s="134"/>
+      <c r="L46" s="134"/>
+      <c r="M46" s="135"/>
+      <c r="O46" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="P46" s="115"/>
-      <c r="Q46" s="115"/>
-      <c r="R46" s="115"/>
-      <c r="S46" s="115"/>
+      <c r="P46" s="167"/>
+      <c r="Q46" s="167"/>
+      <c r="R46" s="167"/>
+      <c r="S46" s="167"/>
     </row>
     <row r="47" spans="2:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B47" s="71" t="s">
+      <c r="B47" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="76">
+      <c r="C47" s="72">
         <f>AVERAGE(P24:T24)</f>
         <v>49242.8</v>
       </c>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
       <c r="H47" s="1"/>
       <c r="I47" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J47" s="138">
+      <c r="J47" s="130">
         <f>U24</f>
         <v>60915.020000000004</v>
       </c>
-      <c r="K47" s="139">
+      <c r="K47" s="131">
         <f>C127</f>
         <v>75815</v>
       </c>
-      <c r="L47" s="140">
+      <c r="L47" s="132">
         <f>J47-K47</f>
         <v>-14899.979999999996</v>
       </c>
-      <c r="M47" s="141">
+      <c r="M47" s="133">
         <f>L47/K47</f>
         <v>-0.19653076567961481</v>
       </c>
-      <c r="O47" s="123" t="s">
+      <c r="O47" s="116" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="48" spans="2:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B48" s="71"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="74"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
       <c r="H48" s="1"/>
       <c r="I48" s="7"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="142"/>
-      <c r="L48" s="142"/>
-      <c r="M48" s="143"/>
-      <c r="O48" s="116" t="s">
+      <c r="J48" s="51"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="134"/>
+      <c r="M48" s="135"/>
+      <c r="O48" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="P48" s="117">
+      <c r="P48" s="110">
         <v>59820</v>
       </c>
-      <c r="Q48" s="117">
+      <c r="Q48" s="110">
         <v>62611</v>
       </c>
-      <c r="R48" s="117">
+      <c r="R48" s="110">
         <v>68960</v>
       </c>
     </row>
     <row r="49" spans="2:18" ht="15" x14ac:dyDescent="0.35">
-      <c r="B49" s="71" t="s">
+      <c r="B49" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C49" s="76">
+      <c r="C49" s="72">
         <f>AVERAGE(P18:T18)</f>
         <v>1003.2</v>
       </c>
-      <c r="D49" s="80"/>
-      <c r="E49" s="80"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
       <c r="H49" s="1"/>
       <c r="I49" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J49" s="138">
+      <c r="J49" s="130">
         <f>U18</f>
         <v>109025.44421999999</v>
       </c>
-      <c r="K49" s="139">
+      <c r="K49" s="131">
         <f>C129</f>
         <v>118529</v>
       </c>
-      <c r="L49" s="140">
+      <c r="L49" s="132">
         <f>J49-K49</f>
         <v>-9503.5557800000097</v>
       </c>
-      <c r="M49" s="141">
+      <c r="M49" s="133">
         <f>L49/K49</f>
         <v>-8.01791610491948E-2</v>
       </c>
-      <c r="O49" s="116" t="s">
+      <c r="O49" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="P49" s="117">
+      <c r="P49" s="110">
         <v>60845</v>
       </c>
-      <c r="Q49" s="117">
+      <c r="Q49" s="110">
         <v>58051</v>
       </c>
-      <c r="R49" s="117">
+      <c r="R49" s="110">
         <v>78026</v>
       </c>
     </row>
     <row r="50" spans="2:18" ht="15" x14ac:dyDescent="0.35">
-      <c r="B50" s="71"/>
-      <c r="C50" s="82"/>
-      <c r="D50" s="79"/>
-      <c r="E50" s="79"/>
+      <c r="B50" s="67"/>
+      <c r="C50" s="78"/>
+      <c r="D50" s="75"/>
+      <c r="E50" s="75"/>
       <c r="H50" s="1"/>
       <c r="I50" s="7"/>
-      <c r="J50" s="57"/>
-      <c r="K50" s="56"/>
-      <c r="L50" s="56"/>
-      <c r="M50" s="143"/>
-      <c r="O50" s="116" t="s">
+      <c r="J50" s="53"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="52"/>
+      <c r="M50" s="135"/>
+      <c r="O50" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="P50" s="117">
+      <c r="P50" s="110">
         <v>11128</v>
       </c>
-      <c r="Q50" s="117">
+      <c r="Q50" s="110">
         <v>9822</v>
       </c>
-      <c r="R50" s="117">
+      <c r="R50" s="110">
         <v>10912</v>
       </c>
     </row>
     <row r="51" spans="2:18" ht="15" x14ac:dyDescent="0.35">
-      <c r="B51" s="71" t="s">
+      <c r="B51" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="C51" s="83">
+      <c r="C51" s="79">
         <f>AVERAGE(P19:T19)</f>
         <v>2.8675752329424169E-3</v>
       </c>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
       <c r="H51" s="1"/>
       <c r="I51" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="J51" s="144">
+      <c r="J51" s="136">
         <f>U19</f>
         <v>0.46199999999999997</v>
       </c>
-      <c r="K51" s="145">
+      <c r="K51" s="137">
         <f>C130</f>
         <v>0.28638771032869748</v>
       </c>
-      <c r="L51" s="146">
+      <c r="L51" s="138">
         <f>J51-K51</f>
         <v>0.17561228967130249</v>
       </c>
-      <c r="M51" s="141">
+      <c r="M51" s="133">
         <f>L51/K51</f>
         <v>0.6131977153270507</v>
       </c>
-      <c r="O51" s="123" t="s">
+      <c r="O51" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="P51" s="127">
+      <c r="P51" s="120">
         <f>SUM(P48:P50)</f>
         <v>131793</v>
       </c>
-      <c r="Q51" s="127">
+      <c r="Q51" s="120">
         <f>SUM(Q48:Q50)</f>
         <v>130484</v>
       </c>
-      <c r="R51" s="127">
+      <c r="R51" s="120">
         <f>SUM(R48:R50)</f>
         <v>157898</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="O53" s="123" t="s">
+      <c r="O53" s="116" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B54" s="60" t="s">
+      <c r="B54" s="56" t="s">
         <v>184</v>
       </c>
-      <c r="C54" s="59"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="59"/>
-      <c r="F54" s="59"/>
-      <c r="G54" s="61"/>
-      <c r="H54" s="60" t="s">
+      <c r="C54" s="55"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="I54" s="59"/>
-      <c r="J54" s="59"/>
-      <c r="K54" s="59"/>
-      <c r="L54" s="59"/>
-      <c r="M54" s="59"/>
-      <c r="O54" s="116" t="s">
+      <c r="I54" s="55"/>
+      <c r="J54" s="55"/>
+      <c r="K54" s="55"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="55"/>
+      <c r="O54" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="P54" s="117">
+      <c r="P54" s="110">
         <v>98959</v>
       </c>
-      <c r="Q54" s="117">
+      <c r="Q54" s="110">
         <v>95281</v>
       </c>
-      <c r="R54" s="117">
+      <c r="R54" s="110">
         <v>85750</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
-      <c r="J55" s="61"/>
-      <c r="K55" s="61"/>
-      <c r="L55" s="61"/>
-      <c r="M55" s="61"/>
-      <c r="O55" s="116" t="s">
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="57"/>
+      <c r="M55" s="57"/>
+      <c r="O55" s="109" t="s">
         <v>70</v>
       </c>
-      <c r="P55" s="117">
+      <c r="P55" s="110">
         <v>49142</v>
       </c>
-      <c r="Q55" s="117">
+      <c r="Q55" s="110">
         <v>49848</v>
       </c>
-      <c r="R55" s="117">
+      <c r="R55" s="110">
         <v>50276</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B56" s="62" t="s">
+      <c r="B56" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="64">
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="60">
         <f>T14</f>
         <v>219836</v>
       </c>
-      <c r="G56" s="61"/>
-      <c r="H56" s="62" t="s">
+      <c r="G56" s="57"/>
+      <c r="H56" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="I56" s="63"/>
-      <c r="J56" s="63"/>
-      <c r="K56" s="63"/>
-      <c r="L56" s="63"/>
-      <c r="M56" s="63"/>
-      <c r="O56" s="123" t="s">
+      <c r="I56" s="59"/>
+      <c r="J56" s="59"/>
+      <c r="K56" s="59"/>
+      <c r="L56" s="59"/>
+      <c r="M56" s="59"/>
+      <c r="O56" s="116" t="s">
         <v>71</v>
       </c>
-      <c r="P56" s="127">
+      <c r="P56" s="120">
         <f>SUM(P54:P55)</f>
         <v>148101</v>
       </c>
-      <c r="Q56" s="127">
+      <c r="Q56" s="120">
         <f>SUM(Q54:Q55)</f>
         <v>145129</v>
       </c>
-      <c r="R56" s="127">
+      <c r="R56" s="120">
         <f>SUM(R54:R55)</f>
         <v>136026</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="61"/>
-      <c r="D57" s="61"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="66">
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="62">
         <f>T17</f>
         <v>210352</v>
       </c>
-      <c r="G57" s="61"/>
-      <c r="H57" s="65" t="s">
+      <c r="G57" s="57"/>
+      <c r="H57" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="I57" s="61"/>
-      <c r="J57" s="61"/>
-      <c r="K57" s="61"/>
-      <c r="L57" s="61"/>
-      <c r="M57" s="66">
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
+      <c r="K57" s="57"/>
+      <c r="L57" s="57"/>
+      <c r="M57" s="62">
         <f>F91</f>
         <v>120154</v>
       </c>
-      <c r="O57" s="123" t="s">
+      <c r="O57" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="P57" s="124">
+      <c r="P57" s="117">
         <f>P51+P56</f>
         <v>279894</v>
       </c>
-      <c r="Q57" s="124">
+      <c r="Q57" s="117">
         <f>Q51+Q56</f>
         <v>275613</v>
       </c>
-      <c r="R57" s="124">
+      <c r="R57" s="117">
         <f>R51+R56</f>
         <v>293924</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="67"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="65" t="s">
+      <c r="B58" s="63"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="I58" s="61"/>
-      <c r="J58" s="61"/>
-      <c r="K58" s="61"/>
-      <c r="L58" s="61"/>
-      <c r="M58" s="66">
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
+      <c r="K58" s="57"/>
+      <c r="L58" s="57"/>
+      <c r="M58" s="62">
         <f>F93</f>
         <v>211306</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B59" s="62" t="s">
+      <c r="B59" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C59" s="63"/>
-      <c r="D59" s="63"/>
-      <c r="E59" s="63"/>
-      <c r="F59" s="68"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="67"/>
-      <c r="I59" s="61"/>
-      <c r="J59" s="61"/>
-      <c r="K59" s="61"/>
-      <c r="L59" s="61"/>
-      <c r="M59" s="61"/>
-      <c r="O59" s="123" t="s">
+      <c r="C59" s="59"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="64"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="57"/>
+      <c r="L59" s="57"/>
+      <c r="M59" s="57"/>
+      <c r="O59" s="116" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="60" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="116" t="s">
+      <c r="B60" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="61"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="66">
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="62">
         <f>T22</f>
         <v>31370</v>
       </c>
-      <c r="G60" s="61"/>
-      <c r="H60" s="69" t="s">
+      <c r="G60" s="57"/>
+      <c r="H60" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="I60" s="63"/>
-      <c r="J60" s="63"/>
-      <c r="K60" s="63"/>
-      <c r="L60" s="63"/>
-      <c r="M60" s="70">
+      <c r="I60" s="59"/>
+      <c r="J60" s="59"/>
+      <c r="K60" s="59"/>
+      <c r="L60" s="59"/>
+      <c r="M60" s="66">
         <f>M57+M58</f>
         <v>331460</v>
       </c>
-      <c r="O60" s="116" t="s">
+      <c r="O60" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="P60" s="117">
+      <c r="P60" s="110">
         <v>64849</v>
       </c>
-      <c r="Q60" s="117">
+      <c r="Q60" s="110">
         <v>73812</v>
       </c>
-      <c r="R60" s="117">
+      <c r="R60" s="110">
         <v>83276</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B61" s="116" t="s">
+      <c r="B61" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="66">
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="62">
         <f>T23</f>
         <v>26097</v>
       </c>
-      <c r="G61" s="61"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="61"/>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
-      <c r="L61" s="61"/>
-      <c r="M61" s="71"/>
-      <c r="O61" s="116" t="s">
+      <c r="G61" s="57"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57"/>
+      <c r="K61" s="57"/>
+      <c r="L61" s="57"/>
+      <c r="M61" s="67"/>
+      <c r="O61" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="P61" s="117">
+      <c r="P61" s="110">
         <v>3068</v>
       </c>
-      <c r="Q61" s="117">
+      <c r="Q61" s="110">
         <v>214</v>
       </c>
-      <c r="R61" s="117">
+      <c r="R61" s="110">
         <v>19154</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="65"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="66"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="62" t="s">
+      <c r="B62" s="61"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="62"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="I62" s="63"/>
-      <c r="J62" s="63"/>
-      <c r="K62" s="63"/>
-      <c r="L62" s="63"/>
-      <c r="M62" s="68"/>
-      <c r="O62" s="116" t="s">
+      <c r="I62" s="59"/>
+      <c r="J62" s="59"/>
+      <c r="K62" s="59"/>
+      <c r="L62" s="59"/>
+      <c r="M62" s="64"/>
+      <c r="O62" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="P62" s="117">
+      <c r="P62" s="110">
         <v>11180</v>
       </c>
-      <c r="Q62" s="117">
+      <c r="Q62" s="110">
         <v>11170</v>
       </c>
-      <c r="R62" s="117">
+      <c r="R62" s="110">
         <v>7163</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B63" s="65"/>
-      <c r="C63" s="61"/>
-      <c r="D63" s="61"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="66"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="65" t="s">
+      <c r="B63" s="61"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="62"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="I63" s="61"/>
-      <c r="J63" s="61"/>
-      <c r="K63" s="61"/>
-      <c r="L63" s="61"/>
-      <c r="M63" s="66">
+      <c r="I63" s="57"/>
+      <c r="J63" s="57"/>
+      <c r="K63" s="57"/>
+      <c r="L63" s="57"/>
+      <c r="M63" s="62">
         <f>F97</f>
         <v>157898</v>
       </c>
-      <c r="O63" s="123" t="s">
+      <c r="O63" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="P63" s="127">
+      <c r="P63" s="120">
         <f>SUM(P60:P62)</f>
         <v>79097</v>
       </c>
-      <c r="Q63" s="127">
+      <c r="Q63" s="120">
         <f>SUM(Q60:Q62)</f>
         <v>85196</v>
       </c>
-      <c r="R63" s="127">
+      <c r="R63" s="120">
         <f>SUM(R60:R62)</f>
         <v>109593</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="61"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="72">
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="68">
         <f>SUM(F60:F63)</f>
         <v>57467</v>
       </c>
-      <c r="G64" s="61"/>
-      <c r="H64" s="65" t="s">
+      <c r="G64" s="57"/>
+      <c r="H64" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="I64" s="61"/>
-      <c r="J64" s="61"/>
-      <c r="K64" s="61"/>
-      <c r="L64" s="61"/>
-      <c r="M64" s="66">
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="62">
         <f>F98</f>
         <v>136026</v>
       </c>
-      <c r="O64" s="128" t="s">
+      <c r="O64" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="P64" s="129">
+      <c r="P64" s="122">
         <f>P57+P63</f>
         <v>358991</v>
       </c>
-      <c r="Q64" s="129">
+      <c r="Q64" s="122">
         <f>Q57+Q63</f>
         <v>360809</v>
       </c>
-      <c r="R64" s="129">
+      <c r="R64" s="122">
         <f>R57+R63</f>
         <v>403517</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B65" s="67"/>
-      <c r="C65" s="61"/>
-      <c r="D65" s="61"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="71"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="65" t="s">
+      <c r="B65" s="63"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="I65" s="63"/>
-      <c r="J65" s="63"/>
-      <c r="K65" s="63"/>
-      <c r="L65" s="63"/>
-      <c r="M65" s="66">
+      <c r="I65" s="59"/>
+      <c r="J65" s="59"/>
+      <c r="K65" s="59"/>
+      <c r="L65" s="59"/>
+      <c r="M65" s="62">
         <f>F99</f>
         <v>109593</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="67"/>
-      <c r="C66" s="61"/>
-      <c r="D66" s="61"/>
-      <c r="E66" s="61"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="67"/>
-      <c r="I66" s="61"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="61"/>
-      <c r="L66" s="61"/>
-      <c r="M66" s="61"/>
-      <c r="O66" s="130" t="s">
+      <c r="B66" s="63"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="57"/>
+      <c r="L66" s="57"/>
+      <c r="M66" s="57"/>
+      <c r="O66" s="123" t="s">
         <v>78</v>
       </c>
-      <c r="P66" s="131">
+      <c r="P66" s="124">
         <f>P44-P57-P63</f>
         <v>-38223</v>
       </c>
-      <c r="Q66" s="131">
+      <c r="Q66" s="124">
         <f>Q44-Q57-Q63</f>
         <v>-39703</v>
       </c>
-      <c r="R66" s="131">
+      <c r="R66" s="124">
         <f>R44-R57-R63</f>
         <v>-72057</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="62" t="s">
+      <c r="B67" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="63"/>
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="70">
+      <c r="C67" s="59"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="59"/>
+      <c r="F67" s="66">
         <f>F56-F57-F64</f>
         <v>-47983</v>
       </c>
-      <c r="G67" s="61"/>
-      <c r="H67" s="69" t="s">
+      <c r="G67" s="57"/>
+      <c r="H67" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="63"/>
-      <c r="J67" s="63"/>
-      <c r="K67" s="63"/>
-      <c r="L67" s="63"/>
-      <c r="M67" s="70">
+      <c r="I67" s="59"/>
+      <c r="J67" s="59"/>
+      <c r="K67" s="59"/>
+      <c r="L67" s="59"/>
+      <c r="M67" s="66">
         <f>SUM(M63:M65)</f>
         <v>403517</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A75" s="84" t="s">
+      <c r="A75" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="B75" s="85"/>
-      <c r="C75" s="86"/>
-      <c r="D75" s="86"/>
-      <c r="E75" s="86"/>
-      <c r="F75" s="85"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="82"/>
+      <c r="F75" s="81"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A76" s="73"/>
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
+      <c r="A76" s="69"/>
+      <c r="B76" s="69"/>
+      <c r="C76" s="69"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
     </row>
     <row r="77" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="63" t="s">
+      <c r="A77" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B77" s="58"/>
-      <c r="C77" s="58"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="87">
+      <c r="B77" s="54"/>
+      <c r="C77" s="54"/>
+      <c r="D77" s="54"/>
+      <c r="E77" s="54"/>
+      <c r="F77" s="83">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A78" s="58"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="61"/>
-      <c r="E78" s="61"/>
-      <c r="F78" s="58"/>
+      <c r="A78" s="54"/>
+      <c r="B78" s="57"/>
+      <c r="C78" s="57"/>
+      <c r="D78" s="57"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="54"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A79" s="67" t="s">
+      <c r="A79" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="88">
+      <c r="B79" s="57"/>
+      <c r="C79" s="57"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="84">
         <f>C116</f>
         <v>413876</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B80" s="61"/>
-      <c r="C80" s="61"/>
-      <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="88">
+      <c r="B80" s="57"/>
+      <c r="C80" s="57"/>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="84">
         <f>C118</f>
         <v>219532</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="67" t="s">
+      <c r="A81" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B81" s="61"/>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
-      <c r="E81" s="61"/>
-      <c r="F81" s="88">
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="84">
         <f>C127</f>
         <v>75815</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="67" t="s">
+      <c r="A82" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B82" s="61"/>
-      <c r="C82" s="61"/>
-      <c r="D82" s="61"/>
-      <c r="E82" s="61"/>
-      <c r="F82" s="88">
+      <c r="B82" s="57"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="84">
         <f>C129</f>
         <v>118529</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="67" t="s">
+      <c r="A83" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
-      <c r="F83" s="89">
+      <c r="B83" s="57"/>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="85">
         <f>C130</f>
         <v>0.28638771032869748</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="61"/>
-      <c r="B84" s="61"/>
-      <c r="C84" s="61"/>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="61"/>
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="57"/>
+      <c r="D84" s="57"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="57"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="81"/>
-      <c r="B85" s="81"/>
-      <c r="C85" s="81"/>
-      <c r="D85" s="81"/>
-      <c r="E85" s="81"/>
-      <c r="F85" s="81"/>
+      <c r="A85" s="77"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="77"/>
+      <c r="E85" s="77"/>
+      <c r="F85" s="77"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="61"/>
-      <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
-      <c r="D86" s="61"/>
-      <c r="E86" s="61"/>
-      <c r="F86" s="61"/>
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
     </row>
     <row r="87" spans="1:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="63" t="s">
+      <c r="A87" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B87" s="90"/>
-      <c r="C87" s="61"/>
-      <c r="D87" s="61"/>
-      <c r="E87" s="61"/>
-      <c r="F87" s="87">
+      <c r="B87" s="86"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="83">
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="63"/>
-      <c r="B88" s="90"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="58"/>
+      <c r="A88" s="59"/>
+      <c r="B88" s="86"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="54"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="91" t="s">
+      <c r="A89" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B89" s="61"/>
-      <c r="C89" s="61"/>
-      <c r="D89" s="61"/>
-      <c r="E89" s="61"/>
-      <c r="F89" s="61"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="57"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="57"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="92"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="61"/>
-      <c r="D90" s="61"/>
-      <c r="E90" s="61"/>
-      <c r="F90" s="61"/>
+      <c r="A90" s="88"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="57"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="67" t="s">
+      <c r="A91" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="B91" s="61"/>
-      <c r="C91" s="61"/>
-      <c r="D91" s="61"/>
-      <c r="E91" s="61"/>
-      <c r="F91" s="88">
+      <c r="B91" s="57"/>
+      <c r="C91" s="57"/>
+      <c r="D91" s="57"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="84">
         <f>R37</f>
         <v>120154</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="92"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="61"/>
-      <c r="D92" s="61"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="88"/>
+      <c r="A92" s="88"/>
+      <c r="B92" s="57"/>
+      <c r="C92" s="57"/>
+      <c r="D92" s="57"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="84"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="67" t="s">
+      <c r="A93" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B93" s="61"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="61"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="93">
+      <c r="B93" s="57"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="89">
         <f>R43</f>
         <v>211306</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="67" t="s">
+      <c r="A94" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="94">
+      <c r="B94" s="57"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="90">
         <f>SUM(F91:F93)</f>
         <v>331460</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="73"/>
-      <c r="B95" s="73"/>
-      <c r="C95" s="73"/>
-      <c r="D95" s="73"/>
-      <c r="E95" s="73"/>
-      <c r="F95" s="73"/>
+      <c r="A95" s="69"/>
+      <c r="B95" s="69"/>
+      <c r="C95" s="69"/>
+      <c r="D95" s="69"/>
+      <c r="E95" s="69"/>
+      <c r="F95" s="69"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="91" t="s">
+      <c r="A96" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="71"/>
+      <c r="B96" s="57"/>
+      <c r="C96" s="57"/>
+      <c r="D96" s="57"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="67"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="67" t="s">
+      <c r="A97" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="B97" s="61"/>
-      <c r="C97" s="61"/>
-      <c r="D97" s="61"/>
-      <c r="E97" s="61"/>
-      <c r="F97" s="88">
+      <c r="B97" s="57"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="84">
         <f>R51</f>
         <v>157898</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="67" t="s">
+      <c r="A98" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="88">
+      <c r="B98" s="57"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="84">
         <f>R56</f>
         <v>136026</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B99" s="61"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="88">
+      <c r="B99" s="57"/>
+      <c r="C99" s="57"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="84">
         <f>R63</f>
         <v>109593</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="92"/>
-      <c r="B100" s="61"/>
-      <c r="C100" s="61"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="95"/>
+      <c r="A100" s="88"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="91"/>
     </row>
     <row r="101" spans="1:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="62" t="s">
+      <c r="A101" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B101" s="61"/>
-      <c r="C101" s="61"/>
-      <c r="D101" s="61"/>
-      <c r="E101" s="61"/>
-      <c r="F101" s="94">
+      <c r="B101" s="57"/>
+      <c r="C101" s="57"/>
+      <c r="D101" s="57"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="90">
         <f>SUM(F97:F99)</f>
         <v>403517</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="132" t="s">
+      <c r="A108" s="168" t="s">
         <v>192</v>
       </c>
-      <c r="B108" s="132"/>
-      <c r="C108" s="132"/>
-      <c r="D108" s="132"/>
-      <c r="E108" s="132"/>
-      <c r="F108" s="132"/>
+      <c r="B108" s="168"/>
+      <c r="C108" s="168"/>
+      <c r="D108" s="168"/>
+      <c r="E108" s="168"/>
+      <c r="F108" s="168"/>
     </row>
     <row r="109" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="15" t="s">
         <v>193</v>
       </c>
       <c r="B109"/>
-      <c r="C109" s="133" t="s">
+      <c r="C109" s="125" t="s">
         <v>31</v>
       </c>
       <c r="D109"/>
@@ -12518,14 +14246,14 @@
       <c r="F110"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="51" t="s">
+      <c r="A111" s="164" t="s">
         <v>194</v>
       </c>
-      <c r="B111" s="51"/>
-      <c r="C111" s="51"/>
-      <c r="D111" s="51"/>
-      <c r="E111" s="51"/>
-      <c r="F111" s="51"/>
+      <c r="B111" s="164"/>
+      <c r="C111" s="164"/>
+      <c r="D111" s="164"/>
+      <c r="E111" s="164"/>
+      <c r="F111" s="164"/>
     </row>
     <row r="112" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="15" t="s">
@@ -12542,7 +14270,7 @@
         <v>35</v>
       </c>
       <c r="B113"/>
-      <c r="C113" s="134">
+      <c r="C113" s="126">
         <v>209230</v>
       </c>
       <c r="D113"/>
@@ -12554,7 +14282,7 @@
         <v>36</v>
       </c>
       <c r="B114"/>
-      <c r="C114" s="134">
+      <c r="C114" s="126">
         <v>107709</v>
       </c>
       <c r="D114"/>
@@ -12566,7 +14294,7 @@
         <v>37</v>
       </c>
       <c r="B115"/>
-      <c r="C115" s="134">
+      <c r="C115" s="126">
         <v>96937</v>
       </c>
       <c r="D115"/>
@@ -12578,7 +14306,7 @@
         <v>21</v>
       </c>
       <c r="B116"/>
-      <c r="C116" s="135">
+      <c r="C116" s="127">
         <f>SUM(C113:C115)</f>
         <v>413876</v>
       </c>
@@ -12599,7 +14327,7 @@
         <v>195</v>
       </c>
       <c r="B118"/>
-      <c r="C118" s="134">
+      <c r="C118" s="126">
         <v>219532</v>
       </c>
       <c r="D118"/>
@@ -12611,7 +14339,7 @@
         <v>41</v>
       </c>
       <c r="B119"/>
-      <c r="C119" s="135">
+      <c r="C119" s="127">
         <f>C116-C118</f>
         <v>194344</v>
       </c>
@@ -12655,7 +14383,7 @@
         <v>44</v>
       </c>
       <c r="B123"/>
-      <c r="C123" s="134">
+      <c r="C123" s="126">
         <v>33252</v>
       </c>
       <c r="D123"/>
@@ -12667,7 +14395,7 @@
         <v>45</v>
       </c>
       <c r="B124"/>
-      <c r="C124" s="134">
+      <c r="C124" s="126">
         <v>27663</v>
       </c>
       <c r="D124"/>
@@ -12679,7 +14407,7 @@
         <v>197</v>
       </c>
       <c r="B125"/>
-      <c r="C125" s="134">
+      <c r="C125" s="126">
         <v>11700</v>
       </c>
       <c r="D125"/>
@@ -12691,7 +14419,7 @@
         <v>198</v>
       </c>
       <c r="B126"/>
-      <c r="C126" s="134">
+      <c r="C126" s="126">
         <v>3200</v>
       </c>
       <c r="D126"/>
@@ -12703,7 +14431,7 @@
         <v>15</v>
       </c>
       <c r="B127"/>
-      <c r="C127" s="135">
+      <c r="C127" s="127">
         <f>SUM(C123:C126)</f>
         <v>75815</v>
       </c>
@@ -12724,7 +14452,7 @@
         <v>16</v>
       </c>
       <c r="B129"/>
-      <c r="C129" s="136">
+      <c r="C129" s="128">
         <f>C119-C127</f>
         <v>118529</v>
       </c>
@@ -12754,14 +14482,14 @@
       <c r="F131"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="51" t="s">
+      <c r="A132" s="164" t="s">
         <v>199</v>
       </c>
-      <c r="B132" s="51"/>
-      <c r="C132" s="51"/>
-      <c r="D132" s="51"/>
-      <c r="E132" s="51"/>
-      <c r="F132" s="51"/>
+      <c r="B132" s="164"/>
+      <c r="C132" s="164"/>
+      <c r="D132" s="164"/>
+      <c r="E132" s="164"/>
+      <c r="F132" s="164"/>
     </row>
     <row r="133" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="15" t="s">
@@ -12778,7 +14506,7 @@
         <v>7</v>
       </c>
       <c r="B134"/>
-      <c r="C134" s="134">
+      <c r="C134" s="126">
         <v>153803</v>
       </c>
       <c r="D134"/>
@@ -12790,7 +14518,7 @@
         <v>8</v>
       </c>
       <c r="B135"/>
-      <c r="C135" s="134">
+      <c r="C135" s="126">
         <v>211306</v>
       </c>
       <c r="D135"/>
@@ -12802,7 +14530,7 @@
         <v>9</v>
       </c>
       <c r="B136"/>
-      <c r="C136" s="135">
+      <c r="C136" s="127">
         <f>C134+C135</f>
         <v>365109</v>
       </c>
@@ -12833,7 +14561,7 @@
         <v>11</v>
       </c>
       <c r="B139"/>
-      <c r="C139" s="134">
+      <c r="C139" s="126">
         <v>176392</v>
       </c>
       <c r="D139"/>
@@ -12845,7 +14573,7 @@
         <v>12</v>
       </c>
       <c r="B140"/>
-      <c r="C140" s="134">
+      <c r="C140" s="126">
         <v>135584</v>
       </c>
       <c r="D140"/>
@@ -12857,7 +14585,7 @@
         <v>13</v>
       </c>
       <c r="B141"/>
-      <c r="C141" s="134">
+      <c r="C141" s="126">
         <v>-56959</v>
       </c>
       <c r="D141"/>
@@ -12869,7 +14597,7 @@
         <v>14</v>
       </c>
       <c r="B142"/>
-      <c r="C142" s="135">
+      <c r="C142" s="127">
         <f>C139+C140+C141</f>
         <v>255017</v>
       </c>
@@ -12882,7 +14610,7 @@
         <v>202</v>
       </c>
       <c r="B143"/>
-      <c r="C143" s="137">
+      <c r="C143" s="129">
         <f>C136-C142</f>
         <v>110092</v>
       </c>
@@ -12892,6 +14620,10 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O9:W9"/>
+    <mergeCell ref="O16:W16"/>
+    <mergeCell ref="O21:W21"/>
     <mergeCell ref="A111:F111"/>
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A132:F132"/>
@@ -12899,10 +14631,6 @@
     <mergeCell ref="O26:S26"/>
     <mergeCell ref="O30:S30"/>
     <mergeCell ref="O46:S46"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O9:W9"/>
-    <mergeCell ref="O16:W16"/>
-    <mergeCell ref="O21:W21"/>
   </mergeCells>
   <conditionalFormatting sqref="M43">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
@@ -12953,7 +14681,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{3CFFC380-F439-4551-9099-A2D357CA6A6D}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{C122E464-D76D-4C1B-846F-3099692CD2A6}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -12964,8 +14692,120 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet2!P14:T14</xm:f>
-              <xm:sqref>D43</xm:sqref>
+              <xm:f>'Dashboard 1'!P19:T19</xm:f>
+              <xm:sqref>E51</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{606C3743-9A78-4ECB-80F5-B07D34A3CF3C}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Dashboard 1'!P18:T18</xm:f>
+              <xm:sqref>E49</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{E5928CB4-0B0A-471E-8476-61F065AD1418}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Dashboard 1'!P24:T24</xm:f>
+              <xm:sqref>E47</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{EABFB7DB-5087-4A97-AE83-848441AA51BB}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Dashboard 1'!P17:T17</xm:f>
+              <xm:sqref>E45</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{B1D5AA89-E047-4C7D-919F-329E5EE0E8FD}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Dashboard 1'!P14:T14</xm:f>
+              <xm:sqref>E43</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{B2E66227-88DF-4379-8AC9-D2D3107712D5}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Dashboard 1'!P19:T19</xm:f>
+              <xm:sqref>D51</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{339D033C-6DF8-4448-886C-B118892460AE}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Dashboard 1'!P18:T18</xm:f>
+              <xm:sqref>D49</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{3928D378-9824-4B6C-B048-1426930B462A}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Dashboard 1'!P24:T24</xm:f>
+              <xm:sqref>D47</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -12980,12 +14820,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet2!P17:T17</xm:f>
+              <xm:f>'Dashboard 1'!P17:T17</xm:f>
               <xm:sqref>D45</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{3928D378-9824-4B6C-B048-1426930B462A}">
+        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{3CFFC380-F439-4551-9099-A2D357CA6A6D}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -12996,120 +14836,8 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet2!P24:T24</xm:f>
-              <xm:sqref>D47</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{339D033C-6DF8-4448-886C-B118892460AE}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet2!P18:T18</xm:f>
-              <xm:sqref>D49</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{B2E66227-88DF-4379-8AC9-D2D3107712D5}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet2!P19:T19</xm:f>
-              <xm:sqref>D51</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{B1D5AA89-E047-4C7D-919F-329E5EE0E8FD}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet2!P14:T14</xm:f>
-              <xm:sqref>E43</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{EABFB7DB-5087-4A97-AE83-848441AA51BB}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet2!P17:T17</xm:f>
-              <xm:sqref>E45</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{E5928CB4-0B0A-471E-8476-61F065AD1418}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet2!P24:T24</xm:f>
-              <xm:sqref>E47</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{606C3743-9A78-4ECB-80F5-B07D34A3CF3C}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet2!P18:T18</xm:f>
-              <xm:sqref>E49</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{C122E464-D76D-4C1B-846F-3099692CD2A6}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet2!P19:T19</xm:f>
-              <xm:sqref>E51</xm:sqref>
+              <xm:f>'Dashboard 1'!P14:T14</xm:f>
+              <xm:sqref>D43</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -13121,516 +14849,1486 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F02A4C-C21B-45EA-8422-6D9DB63C880C}">
-  <dimension ref="AB1:AI31"/>
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:AE59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="28" max="28" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="63.21875" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.21875" customWidth="1"/>
+    <col min="17" max="17" width="8.88671875" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="28" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB1" s="51" t="s">
+    <row r="1" spans="2:29" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="172" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="172"/>
+      <c r="K1" s="172"/>
+      <c r="L1" s="172"/>
+      <c r="M1" s="172"/>
+      <c r="N1" s="172"/>
+      <c r="O1" s="172"/>
+      <c r="P1" s="172"/>
+      <c r="Q1" s="172"/>
+      <c r="R1" s="172"/>
+      <c r="S1" s="172"/>
+      <c r="T1" s="172"/>
+      <c r="U1" s="172"/>
+      <c r="V1" s="164" t="s">
         <v>79</v>
       </c>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51"/>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-    </row>
-    <row r="2" spans="28:35" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="AB2" s="19" t="s">
+      <c r="W1" s="164"/>
+      <c r="X1" s="164"/>
+      <c r="Y1" s="164"/>
+      <c r="Z1" s="164"/>
+      <c r="AA1" s="164"/>
+      <c r="AB1" s="164"/>
+      <c r="AC1" s="164"/>
+    </row>
+    <row r="2" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="V2" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="Z2" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB3" s="12" t="s">
+    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="V3" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="AD3" s="21">
+      <c r="X3" s="21">
         <v>164.08</v>
       </c>
-      <c r="AE3" s="21">
+      <c r="Y3" s="21">
         <v>202</v>
       </c>
-      <c r="AF3" s="21">
+      <c r="Z3" s="21">
         <v>260.10000000000002</v>
       </c>
     </row>
-    <row r="4" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB4" s="12" t="s">
+    <row r="4" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="173" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="173"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="173"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="173"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
+      <c r="L4" s="173"/>
+      <c r="M4" s="173"/>
+      <c r="N4" s="173"/>
+      <c r="O4" s="173"/>
+      <c r="P4" s="173"/>
+      <c r="Q4" s="173"/>
+      <c r="R4" s="173"/>
+      <c r="S4" s="173"/>
+      <c r="T4" s="173"/>
+      <c r="V4" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="AD4" s="21">
+      <c r="X4" s="21">
         <v>195</v>
       </c>
-      <c r="AE4" s="21">
+      <c r="Y4" s="21">
         <v>235</v>
       </c>
-      <c r="AF4" s="21">
+      <c r="Z4" s="21">
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB5" s="12" t="s">
+    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="V5" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="AD5" s="21">
+      <c r="X5" s="21">
         <v>210</v>
       </c>
-      <c r="AE5" s="21">
+      <c r="Y5" s="21">
         <v>240</v>
       </c>
-      <c r="AF5" s="21">
+      <c r="Z5" s="21">
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB6" s="12" t="s">
+    <row r="6" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="V6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="AD6" s="21">
+      <c r="X6" s="21">
         <v>215</v>
       </c>
-      <c r="AE6" s="21">
+      <c r="Y6" s="21">
         <v>248</v>
       </c>
-      <c r="AF6" s="21">
+      <c r="Z6" s="21">
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB7" s="12" t="s">
+    <row r="7" spans="2:29" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="B7" s="140" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" s="141"/>
+      <c r="D7" s="142" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="143"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="170" t="s">
+        <v>210</v>
+      </c>
+      <c r="J7" s="170"/>
+      <c r="K7" s="170"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="142"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="143"/>
+      <c r="P7" s="174" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q7" s="174"/>
+      <c r="R7" s="163">
+        <f>X10</f>
+        <v>245</v>
+      </c>
+      <c r="S7" s="145"/>
+      <c r="T7" s="5"/>
+      <c r="V7" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AD7" s="21">
+      <c r="X7" s="21">
         <v>200</v>
       </c>
-      <c r="AE7" s="21">
+      <c r="Y7" s="21">
         <v>245</v>
       </c>
-      <c r="AF7" s="21">
+      <c r="Z7" s="21">
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB9" s="15" t="s">
+    <row r="9" spans="2:29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="171" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="171"/>
+      <c r="H9" s="171"/>
+      <c r="I9" s="171"/>
+      <c r="J9" s="171"/>
+      <c r="K9" s="171"/>
+      <c r="L9" s="171"/>
+      <c r="M9" s="171"/>
+      <c r="N9" s="171"/>
+      <c r="O9" s="171"/>
+      <c r="P9" s="171"/>
+      <c r="Q9" s="171"/>
+      <c r="R9" s="171"/>
+      <c r="S9" s="171"/>
+      <c r="T9" s="171"/>
+      <c r="V9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="AD9" s="20" t="s">
+      <c r="X9" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB10" s="15" t="s">
+    <row r="10" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B10" s="171"/>
+      <c r="C10" s="171"/>
+      <c r="D10" s="171"/>
+      <c r="E10" s="171"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="171"/>
+      <c r="H10" s="171"/>
+      <c r="I10" s="171"/>
+      <c r="J10" s="171"/>
+      <c r="K10" s="171"/>
+      <c r="L10" s="171"/>
+      <c r="M10" s="171"/>
+      <c r="N10" s="171"/>
+      <c r="O10" s="171"/>
+      <c r="P10" s="171"/>
+      <c r="Q10" s="171"/>
+      <c r="R10" s="171"/>
+      <c r="S10" s="171"/>
+      <c r="T10" s="171"/>
+      <c r="V10" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="AD10" s="22">
+      <c r="X10" s="22">
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AD11" s="10" t="s">
+    <row r="11" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B11" s="171"/>
+      <c r="C11" s="171"/>
+      <c r="D11" s="171"/>
+      <c r="E11" s="171"/>
+      <c r="F11" s="171"/>
+      <c r="G11" s="171"/>
+      <c r="H11" s="171"/>
+      <c r="I11" s="171"/>
+      <c r="J11" s="171"/>
+      <c r="K11" s="171"/>
+      <c r="L11" s="171"/>
+      <c r="M11" s="171"/>
+      <c r="N11" s="171"/>
+      <c r="O11" s="171"/>
+      <c r="P11" s="171"/>
+      <c r="Q11" s="171"/>
+      <c r="R11" s="171"/>
+      <c r="S11" s="171"/>
+      <c r="T11" s="171"/>
+      <c r="X11" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="28:35" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="AB13" s="50" t="s">
+    <row r="12" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="156"/>
+      <c r="L12" s="156"/>
+      <c r="M12" s="156"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="156"/>
+      <c r="P12" s="156"/>
+      <c r="Q12" s="156"/>
+      <c r="R12" s="156"/>
+      <c r="S12" s="156"/>
+    </row>
+    <row r="13" spans="2:29" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="V13" s="169" t="s">
         <v>90</v>
       </c>
-      <c r="AC13" s="50"/>
-      <c r="AD13" s="50"/>
-      <c r="AE13" s="50"/>
-      <c r="AF13" s="50"/>
-      <c r="AG13" s="50"/>
-      <c r="AH13" s="50"/>
-      <c r="AI13" s="50"/>
-    </row>
-    <row r="14" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB14" s="10" t="s">
+      <c r="W13" s="169"/>
+      <c r="X13" s="169"/>
+      <c r="Y13" s="169"/>
+      <c r="Z13" s="169"/>
+      <c r="AA13" s="169"/>
+      <c r="AB13" s="169"/>
+      <c r="AC13" s="169"/>
+    </row>
+    <row r="14" spans="2:29" ht="21" x14ac:dyDescent="0.4">
+      <c r="B14" s="6"/>
+      <c r="C14" s="146" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="147"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="147"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="147"/>
+      <c r="J14" s="147"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="148" t="s">
+        <v>212</v>
+      </c>
+      <c r="M14" s="147"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
+      <c r="Q14" s="147"/>
+      <c r="R14" s="147"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="147"/>
+      <c r="V14" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="28:35" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="AB16" s="19"/>
-      <c r="AD16" s="11" t="s">
+    <row r="15" spans="2:29" ht="21" x14ac:dyDescent="0.4">
+      <c r="B15" s="6"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="151"/>
+      <c r="M15" s="152"/>
+      <c r="N15" s="152"/>
+      <c r="O15" s="152"/>
+      <c r="P15" s="152"/>
+      <c r="Q15" s="152"/>
+      <c r="R15" s="152"/>
+      <c r="S15" s="152"/>
+      <c r="T15" s="152"/>
+    </row>
+    <row r="16" spans="2:29" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="V16" s="19"/>
+      <c r="X16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AE16" s="11" t="s">
+      <c r="Y16" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AF16" s="11" t="s">
+      <c r="Z16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AG16" s="11" t="s">
+      <c r="AA16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AH16" s="11" t="s">
+      <c r="AB16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AI16" s="11" t="s">
+      <c r="AC16" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB17" s="51" t="s">
+    <row r="17" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V17" s="164" t="s">
         <v>92</v>
       </c>
-      <c r="AC17" s="51"/>
-      <c r="AD17" s="51"/>
-      <c r="AE17" s="51"/>
-      <c r="AF17" s="51"/>
-      <c r="AG17" s="51"/>
-      <c r="AH17" s="51"/>
-      <c r="AI17" s="51"/>
-    </row>
-    <row r="18" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB18" s="23" t="s">
+      <c r="W17" s="164"/>
+      <c r="X17" s="164"/>
+      <c r="Y17" s="164"/>
+      <c r="Z17" s="164"/>
+      <c r="AA17" s="164"/>
+      <c r="AB17" s="164"/>
+      <c r="AC17" s="164"/>
+    </row>
+    <row r="18" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V18" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="AD18" s="24">
+      <c r="X18" s="24">
         <v>274515</v>
       </c>
-      <c r="AE18" s="24">
+      <c r="Y18" s="24">
         <v>365817</v>
       </c>
-      <c r="AF18" s="24">
+      <c r="Z18" s="24">
         <v>394328</v>
       </c>
-      <c r="AG18" s="24">
+      <c r="AA18" s="24">
         <v>383285</v>
       </c>
-      <c r="AH18" s="24">
+      <c r="AB18" s="24">
         <v>391035</v>
       </c>
-      <c r="AI18" s="16">
+      <c r="AC18" s="16">
         <v>407476</v>
       </c>
     </row>
-    <row r="19" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB19" s="12" t="s">
+    <row r="19" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="X19" s="13">
         <v>169559</v>
       </c>
-      <c r="AE19" s="13">
+      <c r="Y19" s="13">
         <v>212981</v>
       </c>
-      <c r="AF19" s="13">
+      <c r="Z19" s="13">
         <v>223546</v>
       </c>
-      <c r="AG19" s="13">
+      <c r="AA19" s="13">
         <v>214137</v>
       </c>
-      <c r="AH19" s="13">
+      <c r="AB19" s="13">
         <v>210352</v>
       </c>
-      <c r="AI19" s="14">
+      <c r="AC19" s="14">
         <v>219532</v>
       </c>
     </row>
-    <row r="20" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB20" s="23" t="s">
+    <row r="20" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V20" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="AD20" s="24">
+      <c r="X20" s="24">
         <v>104956</v>
       </c>
-      <c r="AE20" s="24">
+      <c r="Y20" s="24">
         <v>152836</v>
       </c>
-      <c r="AF20" s="24">
+      <c r="Z20" s="24">
         <v>170782</v>
       </c>
-      <c r="AG20" s="24">
+      <c r="AA20" s="24">
         <v>169148</v>
       </c>
-      <c r="AH20" s="24">
+      <c r="AB20" s="24">
         <v>180683</v>
       </c>
-      <c r="AI20" s="16">
+      <c r="AC20" s="16">
         <v>187944</v>
       </c>
     </row>
-    <row r="21" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB21" s="12" t="s">
+    <row r="21" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AD21" s="25">
+      <c r="X21" s="25">
         <v>0.38240000000000002</v>
       </c>
-      <c r="AE21" s="25">
+      <c r="Y21" s="25">
         <v>0.4178</v>
       </c>
-      <c r="AF21" s="25">
+      <c r="Z21" s="25">
         <v>0.43309999999999998</v>
       </c>
-      <c r="AG21" s="25">
+      <c r="AA21" s="25">
         <v>0.44119999999999998</v>
       </c>
-      <c r="AH21" s="25">
+      <c r="AB21" s="25">
         <v>0.46210000000000001</v>
       </c>
-      <c r="AI21" s="26">
+      <c r="AC21" s="26">
         <v>0.46139999999999998</v>
       </c>
     </row>
-    <row r="22" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB22" s="12" t="s">
+    <row r="22" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V22" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AD22" s="13">
+      <c r="X22" s="13">
         <v>18752</v>
       </c>
-      <c r="AE22" s="13">
+      <c r="Y22" s="13">
         <v>21914</v>
       </c>
-      <c r="AF22" s="13">
+      <c r="Z22" s="13">
         <v>26251</v>
       </c>
-      <c r="AG22" s="13">
+      <c r="AA22" s="13">
         <v>29915</v>
       </c>
-      <c r="AH22" s="13">
+      <c r="AB22" s="13">
         <v>31370</v>
       </c>
-      <c r="AI22" s="14">
+      <c r="AC22" s="14">
         <v>33252</v>
       </c>
     </row>
-    <row r="23" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB23" s="12" t="s">
+    <row r="23" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V23" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AD23" s="13">
+      <c r="X23" s="13">
         <v>19916</v>
       </c>
-      <c r="AE23" s="13">
+      <c r="Y23" s="13">
         <v>21973</v>
       </c>
-      <c r="AF23" s="13">
+      <c r="Z23" s="13">
         <v>25094</v>
       </c>
-      <c r="AG23" s="13">
+      <c r="AA23" s="13">
         <v>24932</v>
       </c>
-      <c r="AH23" s="13">
+      <c r="AB23" s="13">
         <v>26097</v>
       </c>
-      <c r="AI23" s="14">
+      <c r="AC23" s="14">
         <v>27663</v>
       </c>
     </row>
-    <row r="24" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB24" s="12" t="s">
+    <row r="24" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V24" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AD24" s="13">
+      <c r="X24" s="13">
         <v>38668</v>
       </c>
-      <c r="AE24" s="13">
+      <c r="Y24" s="13">
         <v>43887</v>
       </c>
-      <c r="AF24" s="13">
+      <c r="Z24" s="13">
         <v>51345</v>
       </c>
-      <c r="AG24" s="13">
+      <c r="AA24" s="13">
         <v>54847</v>
       </c>
-      <c r="AH24" s="13">
+      <c r="AB24" s="13">
         <v>57467</v>
       </c>
-      <c r="AI24" s="14">
+      <c r="AC24" s="14">
         <v>60915</v>
       </c>
     </row>
-    <row r="25" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB25" s="23" t="s">
+    <row r="25" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V25" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="AD25" s="24">
+      <c r="X25" s="24">
         <v>66288</v>
       </c>
-      <c r="AE25" s="24">
+      <c r="Y25" s="24">
         <v>108949</v>
       </c>
-      <c r="AF25" s="24">
+      <c r="Z25" s="24">
         <v>119437</v>
       </c>
-      <c r="AG25" s="24">
+      <c r="AA25" s="24">
         <v>114301</v>
       </c>
-      <c r="AH25" s="24">
+      <c r="AB25" s="24">
         <v>123216</v>
       </c>
-      <c r="AI25" s="16">
+      <c r="AC25" s="16">
         <v>127029</v>
       </c>
     </row>
-    <row r="26" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB26" s="12" t="s">
+    <row r="26" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V26" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AD26" s="25">
+      <c r="X26" s="25">
         <v>0.2414</v>
       </c>
-      <c r="AE26" s="25">
+      <c r="Y26" s="25">
         <v>0.29780000000000001</v>
       </c>
-      <c r="AF26" s="25">
+      <c r="Z26" s="25">
         <v>0.3029</v>
       </c>
-      <c r="AG26" s="25">
+      <c r="AA26" s="25">
         <v>0.29809999999999998</v>
       </c>
-      <c r="AH26" s="25">
+      <c r="AB26" s="25">
         <v>0.31509999999999999</v>
       </c>
-      <c r="AI26" s="26">
+      <c r="AC26" s="26">
         <v>0.31180000000000002</v>
       </c>
     </row>
-    <row r="27" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB27" s="12" t="s">
+    <row r="27" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V27" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AD27" s="13">
+      <c r="X27" s="13">
         <v>11278</v>
       </c>
-      <c r="AE27" s="13">
+      <c r="Y27" s="13">
         <v>11284</v>
       </c>
-      <c r="AF27" s="13">
+      <c r="Z27" s="13">
         <v>12331</v>
       </c>
-      <c r="AG27" s="13">
+      <c r="AA27" s="13">
         <v>11519</v>
       </c>
-      <c r="AH27" s="13">
+      <c r="AB27" s="13">
         <v>11445</v>
       </c>
-      <c r="AI27" s="14">
+      <c r="AC27" s="14">
         <v>11700</v>
       </c>
     </row>
-    <row r="28" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB28" s="23" t="s">
+    <row r="28" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V28" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AD28" s="24">
+      <c r="X28" s="24">
         <v>77566</v>
       </c>
-      <c r="AE28" s="24">
+      <c r="Y28" s="24">
         <v>120233</v>
       </c>
-      <c r="AF28" s="24">
+      <c r="Z28" s="24">
         <v>131768</v>
       </c>
-      <c r="AG28" s="24">
+      <c r="AA28" s="24">
         <v>125820</v>
       </c>
-      <c r="AH28" s="24">
+      <c r="AB28" s="24">
         <v>134661</v>
       </c>
-      <c r="AI28" s="16">
+      <c r="AC28" s="16">
         <v>138729</v>
       </c>
     </row>
-    <row r="29" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB29" s="12" t="s">
+    <row r="29" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V29" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AD29" s="25">
+      <c r="X29" s="25">
         <v>0.28249999999999997</v>
       </c>
-      <c r="AE29" s="25">
+      <c r="Y29" s="25">
         <v>0.3286</v>
       </c>
-      <c r="AF29" s="25">
+      <c r="Z29" s="25">
         <v>0.3342</v>
       </c>
-      <c r="AG29" s="25">
+      <c r="AA29" s="25">
         <v>0.32819999999999999</v>
       </c>
-      <c r="AH29" s="25">
+      <c r="AB29" s="25">
         <v>0.34439999999999998</v>
       </c>
-      <c r="AI29" s="26">
+      <c r="AC29" s="26">
         <v>0.34039999999999998</v>
       </c>
     </row>
-    <row r="30" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB30" s="23" t="s">
+    <row r="30" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V30" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AD30" s="24">
+      <c r="X30" s="24">
         <v>57411</v>
       </c>
-      <c r="AE30" s="24">
+      <c r="Y30" s="24">
         <v>94680</v>
       </c>
-      <c r="AF30" s="24">
+      <c r="Z30" s="24">
         <v>99803</v>
       </c>
-      <c r="AG30" s="24">
+      <c r="AA30" s="24">
         <v>96995</v>
       </c>
-      <c r="AH30" s="24">
+      <c r="AB30" s="24">
         <v>93736</v>
       </c>
-      <c r="AI30" s="16">
+      <c r="AC30" s="16">
         <v>97485</v>
       </c>
     </row>
-    <row r="31" spans="28:35" x14ac:dyDescent="0.3">
-      <c r="AB31" s="12" t="s">
+    <row r="31" spans="22:29" x14ac:dyDescent="0.3">
+      <c r="V31" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AD31" s="25">
+      <c r="X31" s="25">
         <v>0.20910000000000001</v>
       </c>
-      <c r="AE31" s="25">
+      <c r="Y31" s="25">
         <v>0.25890000000000002</v>
       </c>
-      <c r="AF31" s="25">
+      <c r="Z31" s="25">
         <v>0.25309999999999999</v>
       </c>
-      <c r="AG31" s="25">
+      <c r="AA31" s="25">
         <v>0.25309999999999999</v>
       </c>
-      <c r="AH31" s="25">
+      <c r="AB31" s="25">
         <v>0.2397</v>
       </c>
-      <c r="AI31" s="26">
+      <c r="AC31" s="26">
         <v>0.23930000000000001</v>
       </c>
     </row>
+    <row r="33" spans="3:31" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="C33" s="153" t="s">
+        <v>213</v>
+      </c>
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="155"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="155"/>
+      <c r="I33" s="155"/>
+      <c r="J33" s="155"/>
+      <c r="K33" s="149"/>
+      <c r="L33" s="153" t="s">
+        <v>214</v>
+      </c>
+      <c r="M33" s="154"/>
+      <c r="N33" s="154"/>
+      <c r="O33" s="155"/>
+      <c r="P33" s="155"/>
+      <c r="Q33" s="155"/>
+      <c r="R33" s="155"/>
+      <c r="S33" s="155"/>
+      <c r="T33" s="155"/>
+    </row>
+    <row r="34" spans="3:31" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="V34" s="162" t="s">
+        <v>34</v>
+      </c>
+      <c r="W34" s="162"/>
+      <c r="X34" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y34" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z34" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA34" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB34" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC34" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD34" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE34" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V35" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X35" s="13">
+        <v>137781</v>
+      </c>
+      <c r="Y35" s="13">
+        <v>191973</v>
+      </c>
+      <c r="Z35" s="13">
+        <v>205489</v>
+      </c>
+      <c r="AA35" s="13">
+        <v>200583</v>
+      </c>
+      <c r="AB35" s="13">
+        <v>201183</v>
+      </c>
+      <c r="AC35" s="14">
+        <f>AB35*(1+0.04)</f>
+        <v>209230.32</v>
+      </c>
+      <c r="AD35" s="14">
+        <f>AC35*(1+0.04)</f>
+        <v>217599.53280000002</v>
+      </c>
+      <c r="AE35" s="14">
+        <f>AD35*(1+0.04)</f>
+        <v>226303.51411200003</v>
+      </c>
+    </row>
+    <row r="36" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V36" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X36" s="13">
+        <v>28622</v>
+      </c>
+      <c r="Y36" s="13">
+        <v>35190</v>
+      </c>
+      <c r="Z36" s="13">
+        <v>40177</v>
+      </c>
+      <c r="AA36" s="13">
+        <v>29357</v>
+      </c>
+      <c r="AB36" s="13">
+        <v>29984</v>
+      </c>
+      <c r="AC36" s="14">
+        <f>AB36*(1+0.06)</f>
+        <v>31783.040000000001</v>
+      </c>
+      <c r="AD36" s="14">
+        <f>AC36*(1+0.06)</f>
+        <v>33690.022400000002</v>
+      </c>
+      <c r="AE36" s="14">
+        <f>AD36*(1+0.06)</f>
+        <v>35711.423744000007</v>
+      </c>
+    </row>
+    <row r="37" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V37" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="X37" s="157">
+        <v>53768</v>
+      </c>
+      <c r="Y37" s="157">
+        <v>68425</v>
+      </c>
+      <c r="Z37" s="157">
+        <v>78129</v>
+      </c>
+      <c r="AA37" s="157">
+        <v>85200</v>
+      </c>
+      <c r="AB37" s="157">
+        <v>96169</v>
+      </c>
+      <c r="AC37" s="158">
+        <f>AB37*(1+0.12)</f>
+        <v>107709.28000000001</v>
+      </c>
+      <c r="AD37" s="158">
+        <f>AC37*(1+0.12)</f>
+        <v>120634.39360000002</v>
+      </c>
+      <c r="AE37" s="158">
+        <f>AD37*(1+0.12)</f>
+        <v>135110.52083200004</v>
+      </c>
+    </row>
+    <row r="38" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V38" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="X38" s="157">
+        <v>82966</v>
+      </c>
+      <c r="Y38" s="157">
+        <v>105708</v>
+      </c>
+      <c r="Z38" s="157">
+        <v>110711</v>
+      </c>
+      <c r="AA38" s="157">
+        <v>97502</v>
+      </c>
+      <c r="AB38" s="157">
+        <v>93683</v>
+      </c>
+      <c r="AC38" s="158">
+        <f>AB38*(1+0.03)</f>
+        <v>96493.49</v>
+      </c>
+      <c r="AD38" s="158">
+        <f>AC38*(1+0.03)</f>
+        <v>99388.294700000013</v>
+      </c>
+      <c r="AE38" s="158">
+        <f>AD38*(1+0.03)</f>
+        <v>102369.94354100002</v>
+      </c>
+    </row>
+    <row r="39" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V39" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="X39" s="160">
+        <f t="shared" ref="X39:AE39" si="0">SUM(X36:X38)</f>
+        <v>165356</v>
+      </c>
+      <c r="Y39" s="160">
+        <f t="shared" si="0"/>
+        <v>209323</v>
+      </c>
+      <c r="Z39" s="160">
+        <f t="shared" si="0"/>
+        <v>229017</v>
+      </c>
+      <c r="AA39" s="160">
+        <f t="shared" si="0"/>
+        <v>212059</v>
+      </c>
+      <c r="AB39" s="160">
+        <f t="shared" si="0"/>
+        <v>219836</v>
+      </c>
+      <c r="AC39" s="160">
+        <f t="shared" si="0"/>
+        <v>235985.81</v>
+      </c>
+      <c r="AD39" s="160">
+        <f t="shared" si="0"/>
+        <v>253712.71070000005</v>
+      </c>
+      <c r="AE39" s="160">
+        <f t="shared" si="0"/>
+        <v>273191.88811700005</v>
+      </c>
+    </row>
+    <row r="41" spans="3:31" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="V41" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="W41" s="162"/>
+      <c r="X41" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y41" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z41" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA41" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB41" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC41" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD41" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE41" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V42" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="X42" s="13">
+        <v>169559</v>
+      </c>
+      <c r="Y42" s="13">
+        <v>212981</v>
+      </c>
+      <c r="Z42" s="13">
+        <v>223546</v>
+      </c>
+      <c r="AA42" s="13">
+        <v>214137</v>
+      </c>
+      <c r="AB42" s="13">
+        <v>210352</v>
+      </c>
+      <c r="AC42" s="14">
+        <f>AC39*(1-0.462)</f>
+        <v>126960.36578000001</v>
+      </c>
+      <c r="AD42" s="14">
+        <f>AD39*(1-0.455)</f>
+        <v>138273.42733150002</v>
+      </c>
+      <c r="AE42" s="14">
+        <f>AE39*(1-0.45)</f>
+        <v>150255.53846435004</v>
+      </c>
+    </row>
+    <row r="43" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V43" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="X43" s="16">
+        <f t="shared" ref="X43:AE43" si="1">X39-X42</f>
+        <v>-4203</v>
+      </c>
+      <c r="Y43" s="16">
+        <f t="shared" si="1"/>
+        <v>-3658</v>
+      </c>
+      <c r="Z43" s="16">
+        <f t="shared" si="1"/>
+        <v>5471</v>
+      </c>
+      <c r="AA43" s="16">
+        <f t="shared" si="1"/>
+        <v>-2078</v>
+      </c>
+      <c r="AB43" s="16">
+        <f t="shared" si="1"/>
+        <v>9484</v>
+      </c>
+      <c r="AC43" s="16">
+        <f t="shared" si="1"/>
+        <v>109025.44421999999</v>
+      </c>
+      <c r="AD43" s="16">
+        <f t="shared" si="1"/>
+        <v>115439.28336850004</v>
+      </c>
+      <c r="AE43" s="16">
+        <f t="shared" si="1"/>
+        <v>122936.34965265001</v>
+      </c>
+    </row>
+    <row r="44" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V44" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="X44" s="18">
+        <f t="shared" ref="X44:AE44" si="2">IFERROR(X43/X39,"-")</f>
+        <v>-2.541788625752921E-2</v>
+      </c>
+      <c r="Y44" s="18">
+        <f t="shared" si="2"/>
+        <v>-1.7475384931421773E-2</v>
+      </c>
+      <c r="Z44" s="18">
+        <f t="shared" si="2"/>
+        <v>2.3889056270931852E-2</v>
+      </c>
+      <c r="AA44" s="18">
+        <f t="shared" si="2"/>
+        <v>-9.7991596678282927E-3</v>
+      </c>
+      <c r="AB44" s="18">
+        <f t="shared" si="2"/>
+        <v>4.3141250750559509E-2</v>
+      </c>
+      <c r="AC44" s="18">
+        <f t="shared" si="2"/>
+        <v>0.46199999999999997</v>
+      </c>
+      <c r="AD44" s="18">
+        <f t="shared" si="2"/>
+        <v>0.45500000000000007</v>
+      </c>
+      <c r="AE44" s="18">
+        <f t="shared" si="2"/>
+        <v>0.44999999999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="3:31" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="V46" s="162" t="s">
+        <v>215</v>
+      </c>
+      <c r="W46" s="162"/>
+      <c r="X46" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y46" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z46" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA46" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB46" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC46" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD46" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE46" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V47" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="X47" s="24">
+        <v>66288</v>
+      </c>
+      <c r="Y47" s="24">
+        <v>108949</v>
+      </c>
+      <c r="Z47" s="24">
+        <v>119437</v>
+      </c>
+      <c r="AA47" s="24">
+        <v>114301</v>
+      </c>
+      <c r="AB47" s="24">
+        <v>123216</v>
+      </c>
+      <c r="AC47" s="16">
+        <f>AB38-AB44</f>
+        <v>93682.956858749254</v>
+      </c>
+      <c r="AD47" s="16">
+        <f>AC38-AC44</f>
+        <v>96493.028000000006</v>
+      </c>
+      <c r="AE47" s="16">
+        <f>AD38-AD44</f>
+        <v>99387.839700000011</v>
+      </c>
+    </row>
+    <row r="48" spans="3:31" x14ac:dyDescent="0.3">
+      <c r="V48" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="X48" s="18" t="str">
+        <f t="shared" ref="X48:AE48" si="3">IFERROR(X47/X34,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y48" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="Z48" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="AA48" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="AB48" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="AC48" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="AD48" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="AE48" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="49" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V49" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="X49" s="13">
+        <v>11278</v>
+      </c>
+      <c r="Y49" s="13">
+        <v>11284</v>
+      </c>
+      <c r="Z49" s="13">
+        <v>12331</v>
+      </c>
+      <c r="AA49" s="13">
+        <v>11519</v>
+      </c>
+      <c r="AB49" s="13">
+        <v>11445</v>
+      </c>
+      <c r="AC49" s="13">
+        <v>11500</v>
+      </c>
+      <c r="AD49" s="13">
+        <v>11700</v>
+      </c>
+      <c r="AE49" s="13">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="50" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V50" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="X50" s="16">
+        <f t="shared" ref="X50:AE50" si="4">X47+X49</f>
+        <v>77566</v>
+      </c>
+      <c r="Y50" s="16">
+        <f t="shared" si="4"/>
+        <v>120233</v>
+      </c>
+      <c r="Z50" s="16">
+        <f t="shared" si="4"/>
+        <v>131768</v>
+      </c>
+      <c r="AA50" s="16">
+        <f t="shared" si="4"/>
+        <v>125820</v>
+      </c>
+      <c r="AB50" s="16">
+        <f t="shared" si="4"/>
+        <v>134661</v>
+      </c>
+      <c r="AC50" s="16">
+        <f t="shared" si="4"/>
+        <v>105182.95685874925</v>
+      </c>
+      <c r="AD50" s="16">
+        <f t="shared" si="4"/>
+        <v>108193.02800000001</v>
+      </c>
+      <c r="AE50" s="16">
+        <f t="shared" si="4"/>
+        <v>111287.83970000001</v>
+      </c>
+    </row>
+    <row r="51" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V51" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="X51" s="18" t="str">
+        <f t="shared" ref="X51:AE51" si="5">IFERROR(X50/X34,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y51" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="Z51" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="AA51" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="AB51" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="AC51" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="AD51" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="AE51" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="52" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V52" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="X52" s="24">
+        <v>57411</v>
+      </c>
+      <c r="Y52" s="24">
+        <v>94680</v>
+      </c>
+      <c r="Z52" s="24">
+        <v>99803</v>
+      </c>
+      <c r="AA52" s="24">
+        <v>96995</v>
+      </c>
+      <c r="AB52" s="24">
+        <v>93736</v>
+      </c>
+      <c r="AC52" s="16">
+        <f>AB47*0.75</f>
+        <v>92412</v>
+      </c>
+      <c r="AD52" s="16">
+        <f>AC47*0.75</f>
+        <v>70262.217644061937</v>
+      </c>
+      <c r="AE52" s="16">
+        <f>AD47*0.75</f>
+        <v>72369.771000000008</v>
+      </c>
+    </row>
+    <row r="53" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V53" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="X53" s="18" t="str">
+        <f t="shared" ref="X53:AE53" si="6">IFERROR(X52/X34,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y53" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="Z53" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="AA53" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="AB53" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="AC53" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="AD53" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="AE53" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56" spans="22:31" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="V56" s="162" t="s">
+        <v>216</v>
+      </c>
+      <c r="W56" s="162"/>
+      <c r="X56" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y56" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z56" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA56" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB56" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC56" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD56" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE56" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V57" s="161" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y57" s="26">
+        <f>IFERROR((Y35-X35)/X35,"-")</f>
+        <v>0.39331983364905176</v>
+      </c>
+      <c r="Z57" s="26">
+        <f>IFERROR((Z35-Y35)/Y35,"-")</f>
+        <v>7.0405734139696724E-2</v>
+      </c>
+      <c r="AA57" s="26">
+        <f t="shared" ref="AA57:AE57" si="7">IFERROR((AA35-Z35)/Z35,"-")</f>
+        <v>-2.3874757286278098E-2</v>
+      </c>
+      <c r="AB57" s="26">
+        <f t="shared" si="7"/>
+        <v>2.9912804175827464E-3</v>
+      </c>
+      <c r="AC57" s="26">
+        <f t="shared" si="7"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AD57" s="26">
+        <f t="shared" si="7"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AE57" s="26">
+        <f t="shared" si="7"/>
+        <v>4.0000000000000077E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V58" s="161" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y58" s="26" t="str">
+        <f t="shared" ref="Y58:AE58" si="8">IFERROR((Y51-X51)/X51,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Z58" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="AA58" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="AB58" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="AC58" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="AD58" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="AE58" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="59" spans="22:31" x14ac:dyDescent="0.3">
+      <c r="V59" s="161" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y59" s="26" t="str">
+        <f t="shared" ref="Y59:AE59" si="9">IFERROR((Y53-X53)/X53,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Z59" s="26" t="str">
+        <f t="shared" si="9"/>
+        <v>-</v>
+      </c>
+      <c r="AA59" s="26" t="str">
+        <f t="shared" si="9"/>
+        <v>-</v>
+      </c>
+      <c r="AB59" s="26" t="str">
+        <f t="shared" si="9"/>
+        <v>-</v>
+      </c>
+      <c r="AC59" s="26" t="str">
+        <f t="shared" si="9"/>
+        <v>-</v>
+      </c>
+      <c r="AD59" s="26" t="str">
+        <f t="shared" si="9"/>
+        <v>-</v>
+      </c>
+      <c r="AE59" s="26" t="str">
+        <f t="shared" si="9"/>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="AB1:AI1"/>
-    <mergeCell ref="AB13:AI13"/>
-    <mergeCell ref="AB17:AI17"/>
+  <mergeCells count="8">
+    <mergeCell ref="V1:AC1"/>
+    <mergeCell ref="V13:AC13"/>
+    <mergeCell ref="V17:AC17"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B9:T11"/>
+    <mergeCell ref="D1:U1"/>
+    <mergeCell ref="B4:T4"/>
+    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup scale="48" orientation="portrait" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="21" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588A1862-BDC1-44A4-B96B-2B80B3CB6DB2}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.499984740745262"/>
+  </sheetPr>
   <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13645,28 +16343,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="175" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="176" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
@@ -15098,7 +17796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
         <v>178</v>
       </c>
